--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69312</v>
       </c>
       <c r="K92" t="n">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="93">
@@ -11414,7 +11414,7 @@
         <v>79221</v>
       </c>
       <c r="K92" t="n">
-        <v>622</v>
+        <v>631</v>
       </c>
     </row>
     <row r="93">
@@ -14902,7 +14902,7 @@
         <v>140427</v>
       </c>
       <c r="K92" t="n">
-        <v>38</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93">
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21852,7 +21852,7 @@
         <v>189345</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93">
@@ -25327,7 +25327,7 @@
         <v>61273</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
@@ -28802,7 +28802,7 @@
         <v>66065</v>
       </c>
       <c r="K92" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="93">
@@ -32277,7 +32277,7 @@
         <v>54759</v>
       </c>
       <c r="K92" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -35752,7 +35752,7 @@
         <v>56306</v>
       </c>
       <c r="K92" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93">
@@ -39227,7 +39227,7 @@
         <v>52792</v>
       </c>
       <c r="K92" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69312</v>
       </c>
       <c r="K92" t="n">
-        <v>464</v>
+        <v>476</v>
       </c>
     </row>
     <row r="93">
@@ -11414,7 +11414,7 @@
         <v>79221</v>
       </c>
       <c r="K92" t="n">
-        <v>631</v>
+        <v>651</v>
       </c>
     </row>
     <row r="93">
@@ -14902,7 +14902,7 @@
         <v>140427</v>
       </c>
       <c r="K92" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93">
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21852,7 +21852,7 @@
         <v>189345</v>
       </c>
       <c r="K92" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93">
@@ -25327,7 +25327,7 @@
         <v>61273</v>
       </c>
       <c r="K92" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">
@@ -28802,7 +28802,7 @@
         <v>66065</v>
       </c>
       <c r="K92" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93">
@@ -32277,7 +32277,7 @@
         <v>54759</v>
       </c>
       <c r="K92" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93">
@@ -35752,7 +35752,7 @@
         <v>56306</v>
       </c>
       <c r="K92" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93">
@@ -39227,7 +39227,7 @@
         <v>52792</v>
       </c>
       <c r="K92" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7912,13 +7912,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>755277</v>
+        <v>757546</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>0.003004195811602895</v>
       </c>
       <c r="E92" t="n">
         <v>5</v>
@@ -7936,10 +7936,10 @@
         <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69312</v>
+        <v>69343</v>
       </c>
       <c r="K92" t="n">
-        <v>476</v>
+        <v>454</v>
       </c>
     </row>
     <row r="93">
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>133520</v>
+        <v>135789</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>294064</v>
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69312</v>
+        <v>69343</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11414,7 +11414,7 @@
         <v>79221</v>
       </c>
       <c r="K92" t="n">
-        <v>651</v>
+        <v>662</v>
       </c>
     </row>
     <row r="93">
@@ -14899,10 +14899,10 @@
         <v>0.004969606199330583</v>
       </c>
       <c r="J92" t="n">
-        <v>140427</v>
+        <v>140582</v>
       </c>
       <c r="K92" t="n">
-        <v>159</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140427</v>
+        <v>140582</v>
       </c>
     </row>
   </sheetData>
@@ -18359,7 +18359,7 @@
         <v>0.004658180367908079</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>534752</v>
@@ -18374,10 +18374,10 @@
         <v>0.07983473821812527</v>
       </c>
       <c r="J92" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="K92" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="93">
@@ -18399,7 +18399,7 @@
         <v>231827</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
     </row>
   </sheetData>
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189345</v>
+        <v>189409</v>
       </c>
       <c r="K92" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93">
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189345</v>
+        <v>189409</v>
       </c>
     </row>
   </sheetData>
@@ -25309,7 +25309,7 @@
         <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -25324,10 +25324,10 @@
         <v>0.003706420601521177</v>
       </c>
       <c r="J92" t="n">
-        <v>61273</v>
+        <v>61348</v>
       </c>
       <c r="K92" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -25349,7 +25349,7 @@
         <v>80609</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61273</v>
+        <v>61348</v>
       </c>
     </row>
   </sheetData>
@@ -28802,7 +28802,7 @@
         <v>66065</v>
       </c>
       <c r="K92" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="93">
@@ -32274,10 +32274,10 @@
         <v>0.004480147418732545</v>
       </c>
       <c r="J92" t="n">
-        <v>54759</v>
+        <v>54777</v>
       </c>
       <c r="K92" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -32299,7 +32299,7 @@
         <v>51058</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54759</v>
+        <v>54777</v>
       </c>
     </row>
   </sheetData>
@@ -35734,7 +35734,7 @@
         <v>0.0003014396758920605</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
         <v>358699</v>
@@ -35749,10 +35749,10 @@
         <v>0.03095416060413414</v>
       </c>
       <c r="J92" t="n">
-        <v>56306</v>
+        <v>56348</v>
       </c>
       <c r="K92" t="n">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93">
@@ -35774,7 +35774,7 @@
         <v>28881</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>56306</v>
+        <v>56348</v>
       </c>
     </row>
   </sheetData>
@@ -39227,7 +39227,7 @@
         <v>52792</v>
       </c>
       <c r="K92" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7936,10 +7936,10 @@
         <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69343</v>
+        <v>69391</v>
       </c>
       <c r="K92" t="n">
-        <v>454</v>
+        <v>416</v>
       </c>
     </row>
     <row r="93">
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69343</v>
+        <v>69391</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -14899,10 +14899,10 @@
         <v>0.004969606199330583</v>
       </c>
       <c r="J92" t="n">
-        <v>140582</v>
+        <v>140610</v>
       </c>
       <c r="K92" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140582</v>
+        <v>140610</v>
       </c>
     </row>
   </sheetData>
@@ -18359,7 +18359,7 @@
         <v>0.004658180367908079</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
         <v>534752</v>
@@ -18377,7 +18377,7 @@
         <v>79202</v>
       </c>
       <c r="K92" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21852,7 +21852,7 @@
         <v>189409</v>
       </c>
       <c r="K92" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93">
@@ -25309,7 +25309,7 @@
         <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -25324,10 +25324,10 @@
         <v>0.003706420601521177</v>
       </c>
       <c r="J92" t="n">
-        <v>61348</v>
+        <v>61359</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -25349,7 +25349,7 @@
         <v>80609</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61348</v>
+        <v>61359</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F92" t="n">
         <v>499378</v>
@@ -28799,10 +28799,10 @@
         <v>0.0004999621739144736</v>
       </c>
       <c r="J92" t="n">
-        <v>66065</v>
+        <v>66064</v>
       </c>
       <c r="K92" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="93">
@@ -28824,7 +28824,7 @@
         <v>102317</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>66065</v>
+        <v>66064</v>
       </c>
     </row>
   </sheetData>
@@ -32259,7 +32259,7 @@
         <v>-0.007410983976554341</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F92" t="n">
         <v>297725</v>
@@ -32274,10 +32274,10 @@
         <v>0.004480147418732545</v>
       </c>
       <c r="J92" t="n">
-        <v>54777</v>
+        <v>54779</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -32299,7 +32299,7 @@
         <v>51058</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54777</v>
+        <v>54779</v>
       </c>
     </row>
   </sheetData>
@@ -35734,7 +35734,7 @@
         <v>0.0003014396758920605</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F92" t="n">
         <v>358699</v>
@@ -35749,10 +35749,10 @@
         <v>0.03095416060413414</v>
       </c>
       <c r="J92" t="n">
-        <v>56348</v>
+        <v>56412</v>
       </c>
       <c r="K92" t="n">
-        <v>150</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93">
@@ -35774,7 +35774,7 @@
         <v>28881</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>56348</v>
+        <v>56412</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -14875,19 +14875,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1714859</v>
+        <v>1724044</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.009005897433030921</v>
+        <v>0.01441025963885798</v>
       </c>
       <c r="E92" t="n">
         <v>21</v>
       </c>
       <c r="F92" t="n">
-        <v>1165038</v>
+        <v>1169572</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -14896,7 +14896,7 @@
         <v>115237</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.004969606199330583</v>
+        <v>0.008528632341766986</v>
       </c>
       <c r="J92" t="n">
         <v>140610</v>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>507508</v>
+        <v>516693</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>622442</v>
+        <v>626976</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189409</v>
+        <v>189415</v>
       </c>
       <c r="K92" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93">
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189409</v>
+        <v>189415</v>
       </c>
     </row>
   </sheetData>
@@ -25309,7 +25309,7 @@
         <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -35725,13 +35725,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>746643</v>
+        <v>746955</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.0003014396758920605</v>
+        <v>0.0007194360264623843</v>
       </c>
       <c r="E92" t="n">
         <v>13</v>
@@ -35749,10 +35749,10 @@
         <v>0.03095416060413414</v>
       </c>
       <c r="J92" t="n">
-        <v>56412</v>
+        <v>56430</v>
       </c>
       <c r="K92" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93">
@@ -35762,7 +35762,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>255712</v>
+        <v>256024</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>277278</v>
@@ -35774,7 +35774,7 @@
         <v>28881</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>56412</v>
+        <v>56430</v>
       </c>
     </row>
   </sheetData>
@@ -39209,7 +39209,7 @@
         <v>-0.02205260520257466</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7921,7 +7921,7 @@
         <v>0.003004195811602895</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
         <v>514725</v>
@@ -7936,10 +7936,10 @@
         <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69391</v>
+        <v>69411</v>
       </c>
       <c r="K92" t="n">
-        <v>416</v>
+        <v>397</v>
       </c>
     </row>
     <row r="93">
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69391</v>
+        <v>69411</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11411,10 +11411,10 @@
         <v>-0.0002615344732259818</v>
       </c>
       <c r="J92" t="n">
-        <v>79221</v>
+        <v>79239</v>
       </c>
       <c r="K92" t="n">
-        <v>662</v>
+        <v>644</v>
       </c>
     </row>
     <row r="93">
@@ -11436,7 +11436,7 @@
         <v>94589</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>79221</v>
+        <v>79239</v>
       </c>
     </row>
   </sheetData>
@@ -14875,16 +14875,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1724044</v>
+        <v>1727736</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.01441025963885798</v>
+        <v>0.01658259554129821</v>
       </c>
       <c r="E92" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F92" t="n">
         <v>1169572</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>516693</v>
+        <v>520385</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>626976</v>
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189415</v>
+        <v>189410</v>
       </c>
       <c r="K92" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93">
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189415</v>
+        <v>189410</v>
       </c>
     </row>
   </sheetData>
@@ -25309,7 +25309,7 @@
         <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F92" t="n">
         <v>499378</v>
@@ -32259,7 +32259,7 @@
         <v>-0.007410983976554341</v>
       </c>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F92" t="n">
         <v>297725</v>
@@ -35734,7 +35734,7 @@
         <v>0.0007194360264623843</v>
       </c>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F92" t="n">
         <v>358699</v>
@@ -35749,10 +35749,10 @@
         <v>0.03095416060413414</v>
       </c>
       <c r="J92" t="n">
-        <v>56430</v>
+        <v>56443</v>
       </c>
       <c r="K92" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93">
@@ -35774,7 +35774,7 @@
         <v>28881</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>56430</v>
+        <v>56443</v>
       </c>
     </row>
   </sheetData>
@@ -39209,7 +39209,7 @@
         <v>-0.02205260520257466</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7936,10 +7936,10 @@
         <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69411</v>
+        <v>69422</v>
       </c>
       <c r="K92" t="n">
-        <v>397</v>
+        <v>386</v>
       </c>
     </row>
     <row r="93">
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69411</v>
+        <v>69422</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -14875,16 +14875,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1727736</v>
+        <v>1728794</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.01658259554129821</v>
+        <v>0.01720511216772881</v>
       </c>
       <c r="E92" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F92" t="n">
         <v>1169572</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>520385</v>
+        <v>521443</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>626976</v>
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189410</v>
+        <v>189433</v>
       </c>
       <c r="K92" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189410</v>
+        <v>189433</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F92" t="n">
         <v>499378</v>
@@ -35734,7 +35734,7 @@
         <v>0.0007194360264623843</v>
       </c>
       <c r="E92" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F92" t="n">
         <v>358699</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -35752,7 +35752,7 @@
         <v>56443</v>
       </c>
       <c r="K92" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7936,7 +7936,7 @@
         <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69422</v>
+        <v>69419</v>
       </c>
       <c r="K92" t="n">
         <v>386</v>
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69422</v>
+        <v>69419</v>
       </c>
     </row>
   </sheetData>
@@ -14899,7 +14899,7 @@
         <v>0.008528632341766986</v>
       </c>
       <c r="J92" t="n">
-        <v>140610</v>
+        <v>140611</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140610</v>
+        <v>140611</v>
       </c>
     </row>
   </sheetData>
@@ -18374,7 +18374,7 @@
         <v>0.07983473821812527</v>
       </c>
       <c r="J92" t="n">
-        <v>79202</v>
+        <v>79204</v>
       </c>
       <c r="K92" t="n">
         <v>402</v>
@@ -18399,7 +18399,7 @@
         <v>231827</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>79202</v>
+        <v>79204</v>
       </c>
     </row>
   </sheetData>
@@ -21834,7 +21834,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,7 +21849,7 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189433</v>
+        <v>189442</v>
       </c>
       <c r="K92" t="n">
         <v>20</v>
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189433</v>
+        <v>189442</v>
       </c>
     </row>
   </sheetData>
@@ -28799,7 +28799,7 @@
         <v>0.0004999621739144736</v>
       </c>
       <c r="J92" t="n">
-        <v>66064</v>
+        <v>66063</v>
       </c>
       <c r="K92" t="n">
         <v>311</v>
@@ -28824,7 +28824,7 @@
         <v>102317</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>66064</v>
+        <v>66063</v>
       </c>
     </row>
   </sheetData>
@@ -39224,7 +39224,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>52792</v>
+        <v>52796</v>
       </c>
       <c r="K92" t="n">
         <v>63</v>
@@ -39249,7 +39249,7 @@
         <v>72</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>52792</v>
+        <v>52796</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$92</f>
+              <f>'PNB'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$B$2:$B$92</f>
+              <f>'PNB'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -224,12 +224,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$92</f>
+              <f>'PNB'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$F$2:$F$92</f>
+              <f>'PNB'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -255,12 +255,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$92</f>
+              <f>'PNB'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$G$2:$G$92</f>
+              <f>'PNB'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -286,12 +286,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$92</f>
+              <f>'PNB'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$H$2:$H$92</f>
+              <f>'PNB'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -371,12 +371,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$92</f>
+              <f>'JIM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$J$2:$J$92</f>
+              <f>'JIM'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$92</f>
+              <f>'JIM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$K$2:$K$92</f>
+              <f>'JIM'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -486,12 +486,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$92</f>
+              <f>'NDI'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$B$2:$B$92</f>
+              <f>'NDI'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -516,12 +516,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$92</f>
+              <f>'NDI'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$F$2:$F$92</f>
+              <f>'NDI'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -547,12 +547,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$92</f>
+              <f>'NDI'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$G$2:$G$92</f>
+              <f>'NDI'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -578,12 +578,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$92</f>
+              <f>'NDI'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$H$2:$H$92</f>
+              <f>'NDI'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -663,12 +663,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$92</f>
+              <f>'NDI'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$J$2:$J$92</f>
+              <f>'NDI'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -693,12 +693,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$92</f>
+              <f>'NDI'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$K$2:$K$92</f>
+              <f>'NDI'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -778,12 +778,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$92</f>
+              <f>'CXM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$B$2:$B$92</f>
+              <f>'CXM'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -808,12 +808,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$92</f>
+              <f>'CXM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$F$2:$F$92</f>
+              <f>'CXM'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -839,12 +839,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$92</f>
+              <f>'CXM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$G$2:$G$92</f>
+              <f>'CXM'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -870,12 +870,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$92</f>
+              <f>'CXM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$H$2:$H$92</f>
+              <f>'CXM'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -955,12 +955,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$92</f>
+              <f>'CXM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$J$2:$J$92</f>
+              <f>'CXM'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -985,12 +985,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$92</f>
+              <f>'CXM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$K$2:$K$92</f>
+              <f>'CXM'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1070,12 +1070,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$92</f>
+              <f>'AUA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$B$2:$B$92</f>
+              <f>'AUA'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1100,12 +1100,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$92</f>
+              <f>'AUA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$F$2:$F$92</f>
+              <f>'AUA'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$92</f>
+              <f>'AUA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$G$2:$G$92</f>
+              <f>'AUA'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1162,12 +1162,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$92</f>
+              <f>'AUA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$H$2:$H$92</f>
+              <f>'AUA'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1247,12 +1247,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$92</f>
+              <f>'AUA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$J$2:$J$92</f>
+              <f>'AUA'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1277,12 +1277,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$92</f>
+              <f>'AUA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$K$2:$K$92</f>
+              <f>'AUA'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1362,12 +1362,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$92</f>
+              <f>'CMA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$B$2:$B$92</f>
+              <f>'CMA'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1392,12 +1392,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$92</f>
+              <f>'CMA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$F$2:$F$92</f>
+              <f>'CMA'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$92</f>
+              <f>'CMA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$G$2:$G$92</f>
+              <f>'CMA'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1454,12 +1454,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$92</f>
+              <f>'CMA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$H$2:$H$92</f>
+              <f>'CMA'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1539,12 +1539,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$92</f>
+              <f>'CMA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$J$2:$J$92</f>
+              <f>'CMA'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1569,12 +1569,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$92</f>
+              <f>'CMA'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$K$2:$K$92</f>
+              <f>'CMA'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1654,12 +1654,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$92</f>
+              <f>'PPR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$B$2:$B$92</f>
+              <f>'PPR'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1684,12 +1684,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$92</f>
+              <f>'PPR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$F$2:$F$92</f>
+              <f>'PPR'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1715,12 +1715,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$92</f>
+              <f>'PPR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$G$2:$G$92</f>
+              <f>'PPR'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1746,12 +1746,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$92</f>
+              <f>'PPR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$H$2:$H$92</f>
+              <f>'PPR'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1831,12 +1831,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$92</f>
+              <f>'PNB'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$J$2:$J$92</f>
+              <f>'PNB'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1861,12 +1861,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$92</f>
+              <f>'PNB'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$K$2:$K$92</f>
+              <f>'PNB'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1946,12 +1946,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$92</f>
+              <f>'PPR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$J$2:$J$92</f>
+              <f>'PPR'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -1976,12 +1976,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$92</f>
+              <f>'PPR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$K$2:$K$92</f>
+              <f>'PPR'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2061,12 +2061,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$92</f>
+              <f>'TLS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$B$2:$B$92</f>
+              <f>'TLS'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2091,12 +2091,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$92</f>
+              <f>'TLS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$F$2:$F$92</f>
+              <f>'TLS'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2122,12 +2122,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$92</f>
+              <f>'TLS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$G$2:$G$92</f>
+              <f>'TLS'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$92</f>
+              <f>'TLS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$H$2:$H$92</f>
+              <f>'TLS'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2238,12 +2238,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$92</f>
+              <f>'TLS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$J$2:$J$92</f>
+              <f>'TLS'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2268,12 +2268,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$92</f>
+              <f>'TLS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$K$2:$K$92</f>
+              <f>'TLS'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2353,12 +2353,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$92</f>
+              <f>'NVR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$B$2:$B$92</f>
+              <f>'NVR'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2383,12 +2383,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$92</f>
+              <f>'NVR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$F$2:$F$92</f>
+              <f>'NVR'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2414,12 +2414,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$92</f>
+              <f>'NVR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$G$2:$G$92</f>
+              <f>'NVR'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2445,12 +2445,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$92</f>
+              <f>'NVR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$H$2:$H$92</f>
+              <f>'NVR'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2530,12 +2530,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$92</f>
+              <f>'NVR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$J$2:$J$92</f>
+              <f>'NVR'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2560,12 +2560,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$92</f>
+              <f>'NVR'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$K$2:$K$92</f>
+              <f>'NVR'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2645,12 +2645,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$92</f>
+              <f>'DOS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$B$2:$B$92</f>
+              <f>'DOS'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2675,12 +2675,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$92</f>
+              <f>'DOS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$F$2:$F$92</f>
+              <f>'DOS'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2706,12 +2706,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$92</f>
+              <f>'DOS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$G$2:$G$92</f>
+              <f>'DOS'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2737,12 +2737,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$92</f>
+              <f>'DOS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$H$2:$H$92</f>
+              <f>'DOS'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2822,12 +2822,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$92</f>
+              <f>'DOS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$J$2:$J$92</f>
+              <f>'DOS'!$J$2:$J$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2852,12 +2852,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$92</f>
+              <f>'DOS'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$K$2:$K$92</f>
+              <f>'DOS'!$K$2:$K$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2937,12 +2937,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$92</f>
+              <f>'JIM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$B$2:$B$92</f>
+              <f>'JIM'!$B$2:$B$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2967,12 +2967,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$92</f>
+              <f>'JIM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$F$2:$F$92</f>
+              <f>'JIM'!$F$2:$F$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -2998,12 +2998,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$92</f>
+              <f>'JIM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$G$2:$G$92</f>
+              <f>'JIM'!$G$2:$G$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -3029,12 +3029,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$92</f>
+              <f>'JIM'!$A$2:$A$93</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$H$2:$H$92</f>
+              <f>'JIM'!$H$2:$H$93</f>
             </numRef>
           </yVal>
         </ser>
@@ -4502,7 +4502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7943,25 +7943,62 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>757546</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>514725</v>
+      </c>
+      <c r="G93" t="n">
+        <v>50527</v>
+      </c>
+      <c r="H93" t="n">
+        <v>28993</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>69488</v>
+      </c>
+      <c r="K93" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>135789</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>294064</v>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="G94" s="6" t="n">
         <v>50527</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>28993</v>
       </c>
-      <c r="J93" s="6" t="n">
-        <v>69419</v>
+      <c r="J94" s="6" t="n">
+        <v>69488</v>
       </c>
     </row>
   </sheetData>
@@ -7977,7 +8014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11396,7 +11433,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11418,25 +11455,62 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1076576</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>750284</v>
+      </c>
+      <c r="G93" t="n">
+        <v>26677</v>
+      </c>
+      <c r="H93" t="n">
+        <v>94589</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>79302</v>
+      </c>
+      <c r="K93" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>227150</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>251377</v>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="G94" s="6" t="n">
         <v>26677</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>94589</v>
       </c>
-      <c r="J93" s="6" t="n">
-        <v>79239</v>
+      <c r="J94" s="6" t="n">
+        <v>79302</v>
       </c>
     </row>
   </sheetData>
@@ -11465,7 +11539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14906,24 +14980,61 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1733828</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0.002911856473356571</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1174070</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>115237</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0.003500909473703873</v>
+      </c>
+      <c r="J93" t="n">
+        <v>140611</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
-        <v>521443</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>626976</v>
-      </c>
-      <c r="G93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="6" t="n">
+      <c r="B94" s="6" t="n">
+        <v>526477</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>631474</v>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6" t="n">
         <v>115237</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J94" s="6" t="n">
         <v>140611</v>
       </c>
     </row>
@@ -14940,7 +15051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18381,24 +18492,61 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1219217</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>534752</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>231827</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>79204</v>
+      </c>
+      <c r="K93" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>89154</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>299895</v>
       </c>
-      <c r="G93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="6" t="n">
+      <c r="G94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6" t="n">
         <v>231827</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J94" s="6" t="n">
         <v>79204</v>
       </c>
     </row>
@@ -18415,7 +18563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21834,7 +21982,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21856,24 +22004,61 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3071345</v>
+      </c>
+      <c r="C93" t="n">
+        <v>50692</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1842767</v>
+      </c>
+      <c r="G93" t="n">
+        <v>123505</v>
+      </c>
+      <c r="H93" t="n">
+        <v>154953</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>189442</v>
+      </c>
+      <c r="K93" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>735524</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>958303</v>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="G94" s="6" t="n">
         <v>123505</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>154953</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J94" s="6" t="n">
         <v>189442</v>
       </c>
     </row>
@@ -21890,7 +22075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25331,25 +25516,62 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>956245</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>590365</v>
+      </c>
+      <c r="G93" t="n">
+        <v>4948</v>
+      </c>
+      <c r="H93" t="n">
+        <v>80609</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>61358</v>
+      </c>
+      <c r="K93" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>227355</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>358194</v>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="G94" s="6" t="n">
         <v>4948</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>80609</v>
       </c>
-      <c r="J93" s="6" t="n">
-        <v>61359</v>
+      <c r="J94" s="6" t="n">
+        <v>61358</v>
       </c>
     </row>
   </sheetData>
@@ -25365,7 +25587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -28806,24 +29028,61 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>935351</v>
+      </c>
+      <c r="C93" t="n">
+        <v>11614</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>499378</v>
+      </c>
+      <c r="G93" t="n">
+        <v>6655</v>
+      </c>
+      <c r="H93" t="n">
+        <v>102317</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>66063</v>
+      </c>
+      <c r="K93" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>92870</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>224466</v>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="G94" s="6" t="n">
         <v>6655</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>102317</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J94" s="6" t="n">
         <v>66063</v>
       </c>
     </row>
@@ -28840,7 +29099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32281,25 +32540,62 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>795573</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>299957</v>
+      </c>
+      <c r="G93" t="n">
+        <v>83</v>
+      </c>
+      <c r="H93" t="n">
+        <v>51058</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0.006397871962300712</v>
+      </c>
+      <c r="J93" t="n">
+        <v>54781</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>101737</v>
       </c>
-      <c r="F93" s="6" t="n">
-        <v>191318</v>
-      </c>
-      <c r="G93" s="6" t="n">
+      <c r="F94" s="6" t="n">
+        <v>193550</v>
+      </c>
+      <c r="G94" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>51058</v>
       </c>
-      <c r="J93" s="6" t="n">
-        <v>54779</v>
+      <c r="J94" s="6" t="n">
+        <v>54781</v>
       </c>
     </row>
   </sheetData>
@@ -32315,7 +32611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -35734,7 +36030,7 @@
         <v>0.0007194360264623843</v>
       </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F92" t="n">
         <v>358699</v>
@@ -35756,24 +36052,61 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>746955</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>358699</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>28881</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>56443</v>
+      </c>
+      <c r="K93" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>256024</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>277278</v>
       </c>
-      <c r="G93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="6" t="n">
+      <c r="G94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6" t="n">
         <v>28881</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J94" s="6" t="n">
         <v>56443</v>
       </c>
     </row>
@@ -35790,7 +36123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39231,24 +39564,61 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>499559</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>295759</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>72</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>52796</v>
+      </c>
+      <c r="K93" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B94" s="6" t="n">
         <v>-111166</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>-7808</v>
       </c>
-      <c r="G93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="6" t="n">
+      <c r="G94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J94" s="6" t="n">
         <v>52796</v>
       </c>
     </row>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>69488</v>
+        <v>69535</v>
       </c>
       <c r="K93" t="n">
-        <v>325</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94">
@@ -7998,7 +7998,7 @@
         <v>28993</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69488</v>
+        <v>69535</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -14986,13 +14986,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1733828</v>
+        <v>1736882</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.002911856473356571</v>
+        <v>0.004678405871376231</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>526477</v>
+        <v>529531</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>631474</v>
@@ -18507,7 +18507,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>534752</v>
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189442</v>
       </c>
       <c r="K93" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
@@ -32546,13 +32546,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>795573</v>
+        <v>795848</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>0.0003456628115836007</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -32570,10 +32570,10 @@
         <v>0.006397871962300712</v>
       </c>
       <c r="J93" t="n">
-        <v>54781</v>
+        <v>54782</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>101737</v>
+        <v>102012</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>193550</v>
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54781</v>
+        <v>54782</v>
       </c>
     </row>
   </sheetData>
@@ -36067,7 +36067,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>358699</v>
@@ -39594,10 +39594,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>52796</v>
+        <v>9611</v>
       </c>
       <c r="K93" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -39619,7 +39619,7 @@
         <v>72</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>52796</v>
+        <v>9611</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7961,22 +7961,22 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>514725</v>
+        <v>561423</v>
       </c>
       <c r="G93" t="n">
-        <v>50527</v>
+        <v>4444</v>
       </c>
       <c r="H93" t="n">
-        <v>28993</v>
+        <v>37576</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0</v>
+        <v>0.01547846426978771</v>
       </c>
       <c r="J93" t="n">
-        <v>69535</v>
+        <v>69551</v>
       </c>
       <c r="K93" t="n">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94">
@@ -7989,16 +7989,16 @@
         <v>135789</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>294064</v>
+        <v>340762</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>50527</v>
+        <v>4444</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>28993</v>
+        <v>37576</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69535</v>
+        <v>69551</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -14995,7 +14995,7 @@
         <v>0.004678405871376231</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>1174070</v>
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -32558,7 +32558,7 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>299957</v>
+        <v>301273</v>
       </c>
       <c r="G93" t="n">
         <v>83</v>
@@ -32567,7 +32567,7 @@
         <v>51058</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.006397871962300712</v>
+        <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
         <v>54782</v>
@@ -32586,7 +32586,7 @@
         <v>102012</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>193550</v>
+        <v>194866</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>83</v>
@@ -39594,10 +39594,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>9611</v>
+        <v>52796</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94">
@@ -39619,7 +39619,7 @@
         <v>72</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>9611</v>
+        <v>52796</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7961,22 +7961,22 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>561423</v>
+        <v>560731</v>
       </c>
       <c r="G93" t="n">
-        <v>4444</v>
+        <v>5908</v>
       </c>
       <c r="H93" t="n">
         <v>37576</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.01547846426978771</v>
+        <v>0.01677759173404909</v>
       </c>
       <c r="J93" t="n">
-        <v>69551</v>
+        <v>69589</v>
       </c>
       <c r="K93" t="n">
-        <v>255</v>
+        <v>220</v>
       </c>
     </row>
     <row r="94">
@@ -7989,16 +7989,16 @@
         <v>135789</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>340762</v>
+        <v>340070</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>4444</v>
+        <v>5908</v>
       </c>
       <c r="H94" s="6" t="n">
         <v>37576</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69551</v>
+        <v>69589</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -32546,13 +32546,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>795848</v>
+        <v>795843</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.0003456628115836007</v>
+        <v>0.0003393780331911716</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>102012</v>
+        <v>102007</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>194866</v>
@@ -36067,7 +36067,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>358699</v>
@@ -39570,13 +39570,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>499559</v>
+        <v>502660</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>0.006207474992943777</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -39607,7 +39607,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>-111166</v>
+        <v>-108065</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>-7808</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7961,22 +7961,22 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>560731</v>
+        <v>560812</v>
       </c>
       <c r="G93" t="n">
         <v>5908</v>
       </c>
       <c r="H93" t="n">
-        <v>37576</v>
+        <v>37852</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.01677759173404909</v>
+        <v>0.01737835404589016</v>
       </c>
       <c r="J93" t="n">
-        <v>69589</v>
+        <v>69570</v>
       </c>
       <c r="K93" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="94">
@@ -7989,16 +7989,16 @@
         <v>135789</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>340070</v>
+        <v>340151</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>5908</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>37576</v>
+        <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69589</v>
+        <v>69570</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -18507,7 +18507,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>534752</v>
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -25546,7 +25546,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61358</v>
+        <v>61357</v>
       </c>
       <c r="K93" t="n">
         <v>96</v>
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61358</v>
+        <v>61357</v>
       </c>
     </row>
   </sheetData>
@@ -29058,7 +29058,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>66063</v>
+        <v>66062</v>
       </c>
       <c r="K93" t="n">
         <v>312</v>
@@ -29083,7 +29083,7 @@
         <v>102317</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>66063</v>
+        <v>66062</v>
       </c>
     </row>
   </sheetData>
@@ -36067,7 +36067,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>358699</v>
@@ -39579,7 +39579,7 @@
         <v>0.006207474992943777</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69570</v>
       </c>
       <c r="K93" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="94">
@@ -11488,7 +11488,7 @@
         <v>79302</v>
       </c>
       <c r="K93" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="94">
@@ -15013,7 +15013,7 @@
         <v>140611</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -18525,7 +18525,7 @@
         <v>79204</v>
       </c>
       <c r="K93" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="94">
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189442</v>
       </c>
       <c r="K93" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94">
@@ -25549,7 +25549,7 @@
         <v>61357</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94">
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94">
@@ -32573,7 +32573,7 @@
         <v>54782</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -36085,7 +36085,7 @@
         <v>56443</v>
       </c>
       <c r="K93" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94">
@@ -39597,7 +39597,7 @@
         <v>52796</v>
       </c>
       <c r="K93" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7973,10 +7973,10 @@
         <v>0.01737835404589016</v>
       </c>
       <c r="J93" t="n">
-        <v>69570</v>
+        <v>69577</v>
       </c>
       <c r="K93" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94">
@@ -7998,7 +7998,7 @@
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69570</v>
+        <v>69577</v>
       </c>
     </row>
   </sheetData>
@@ -11461,13 +11461,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1076576</v>
+        <v>1077298</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>6373</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
         <v>6</v>
@@ -11485,10 +11485,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>79302</v>
+        <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>592</v>
+        <v>457</v>
       </c>
     </row>
     <row r="94">
@@ -11498,7 +11498,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>227150</v>
+        <v>227872</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>251377</v>
@@ -11510,7 +11510,7 @@
         <v>94589</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79302</v>
+        <v>79441</v>
       </c>
     </row>
   </sheetData>
@@ -14998,7 +14998,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>1174070</v>
+        <v>1175586</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -15007,13 +15007,13 @@
         <v>115237</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.003500909473703873</v>
+        <v>0.004680851395032258</v>
       </c>
       <c r="J93" t="n">
-        <v>140611</v>
+        <v>140618</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -15026,7 +15026,7 @@
         <v>529531</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>631474</v>
+        <v>632990</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
         <v>115237</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>140611</v>
+        <v>140618</v>
       </c>
     </row>
   </sheetData>
@@ -18498,13 +18498,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1219217</v>
+        <v>1218673</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>-0.0004461880042683132</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -18525,7 +18525,7 @@
         <v>79204</v>
       </c>
       <c r="K93" t="n">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="94">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>89154</v>
+        <v>88610</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>299895</v>
@@ -21982,7 +21982,7 @@
         <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189442</v>
+        <v>189508</v>
       </c>
       <c r="K93" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94">
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189442</v>
+        <v>189508</v>
       </c>
     </row>
   </sheetData>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61357</v>
+        <v>61362</v>
       </c>
       <c r="K93" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61357</v>
+        <v>61362</v>
       </c>
     </row>
   </sheetData>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="94">
@@ -32546,16 +32546,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>795843</v>
+        <v>795577</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.0003393780331911716</v>
+        <v>5.027822713943284e-06</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -32570,10 +32570,10 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54782</v>
+        <v>54792</v>
       </c>
       <c r="K93" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>102007</v>
+        <v>101741</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>194866</v>
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54782</v>
+        <v>54792</v>
       </c>
     </row>
   </sheetData>
@@ -36067,7 +36067,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F93" t="n">
         <v>358699</v>
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56443</v>
+        <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56443</v>
+        <v>56436</v>
       </c>
     </row>
   </sheetData>
@@ -39579,7 +39579,7 @@
         <v>0.006207474992943777</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>295759</v>
@@ -39597,7 +39597,7 @@
         <v>52796</v>
       </c>
       <c r="K93" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7973,10 +7973,10 @@
         <v>0.01737835404589016</v>
       </c>
       <c r="J93" t="n">
-        <v>69577</v>
+        <v>69572</v>
       </c>
       <c r="K93" t="n">
-        <v>249</v>
+        <v>265</v>
       </c>
     </row>
     <row r="94">
@@ -7998,7 +7998,7 @@
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69577</v>
+        <v>69572</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="94">
@@ -14998,7 +14998,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>1175586</v>
+        <v>1176979</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -15007,13 +15007,13 @@
         <v>115237</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.004680851395032258</v>
+        <v>0.005765059242268695</v>
       </c>
       <c r="J93" t="n">
-        <v>140618</v>
+        <v>140626</v>
       </c>
       <c r="K93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -15026,7 +15026,7 @@
         <v>529531</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>632990</v>
+        <v>634383</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
         <v>115237</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>140618</v>
+        <v>140626</v>
       </c>
     </row>
   </sheetData>
@@ -18525,7 +18525,7 @@
         <v>79204</v>
       </c>
       <c r="K93" t="n">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94">
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189508</v>
+        <v>189589</v>
       </c>
       <c r="K93" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189508</v>
+        <v>189589</v>
       </c>
     </row>
   </sheetData>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61362</v>
+        <v>61367</v>
       </c>
       <c r="K93" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61362</v>
+        <v>61367</v>
       </c>
     </row>
   </sheetData>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="94">
@@ -32546,13 +32546,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>795577</v>
+        <v>797442</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>5.027822713943284e-06</v>
+        <v>0.002349250163089999</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -32570,7 +32570,7 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54792</v>
+        <v>54796</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>101741</v>
+        <v>103606</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>194866</v>
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54792</v>
+        <v>54796</v>
       </c>
     </row>
   </sheetData>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94">
@@ -39594,7 +39594,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>52796</v>
+        <v>52797</v>
       </c>
       <c r="K93" t="n">
         <v>57</v>
@@ -39619,7 +39619,7 @@
         <v>72</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>52796</v>
+        <v>52797</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7973,10 +7973,10 @@
         <v>0.01737835404589016</v>
       </c>
       <c r="J93" t="n">
-        <v>69572</v>
+        <v>69610</v>
       </c>
       <c r="K93" t="n">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94">
@@ -7998,7 +7998,7 @@
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69572</v>
+        <v>69610</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="94">
@@ -14986,16 +14986,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1736882</v>
+        <v>1737792</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.004678405871376231</v>
+        <v>0.005204784375697741</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>1176979</v>
@@ -15010,10 +15010,10 @@
         <v>0.005765059242268695</v>
       </c>
       <c r="J93" t="n">
-        <v>140626</v>
+        <v>140645</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>529531</v>
+        <v>530441</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>634383</v>
@@ -15035,7 +15035,7 @@
         <v>115237</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>140626</v>
+        <v>140645</v>
       </c>
     </row>
   </sheetData>
@@ -18525,7 +18525,7 @@
         <v>79204</v>
       </c>
       <c r="K93" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="94">
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189589</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94">
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61367</v>
+        <v>61366</v>
       </c>
       <c r="K93" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61367</v>
+        <v>61366</v>
       </c>
     </row>
   </sheetData>
@@ -29043,7 +29043,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>499378</v>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94">
@@ -32546,16 +32546,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>797442</v>
+        <v>797563</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.002349250163089999</v>
+        <v>0.002501341800186784</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -32570,7 +32570,7 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54796</v>
+        <v>54802</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>103606</v>
+        <v>103727</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>194866</v>
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54796</v>
+        <v>54802</v>
       </c>
     </row>
   </sheetData>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69610</v>
       </c>
       <c r="K93" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94">
@@ -11488,7 +11488,7 @@
         <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="94">
@@ -15010,7 +15010,7 @@
         <v>0.005765059242268695</v>
       </c>
       <c r="J93" t="n">
-        <v>140645</v>
+        <v>140659</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -15035,7 +15035,7 @@
         <v>115237</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>140645</v>
+        <v>140659</v>
       </c>
     </row>
   </sheetData>
@@ -18498,16 +18498,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1218673</v>
+        <v>1218684</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>-0.0004461880042683132</v>
+        <v>-0.000437165820358476</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>534752</v>
@@ -18525,7 +18525,7 @@
         <v>79204</v>
       </c>
       <c r="K93" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
     </row>
     <row r="94">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>88610</v>
+        <v>88621</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>299895</v>
@@ -22010,16 +22010,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3071345</v>
+        <v>3072569</v>
       </c>
       <c r="C93" t="n">
         <v>50692</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189589</v>
+        <v>189606</v>
       </c>
       <c r="K93" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
@@ -22047,7 +22047,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>735524</v>
+        <v>736748</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>958303</v>
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189589</v>
+        <v>189606</v>
       </c>
     </row>
   </sheetData>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25549,7 +25549,7 @@
         <v>61366</v>
       </c>
       <c r="K93" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94">
@@ -29043,7 +29043,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>499378</v>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94">
@@ -32570,7 +32570,7 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54802</v>
+        <v>54810</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54802</v>
+        <v>54810</v>
       </c>
     </row>
   </sheetData>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94">
@@ -39597,7 +39597,7 @@
         <v>52797</v>
       </c>
       <c r="K93" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69610</v>
       </c>
       <c r="K93" t="n">
-        <v>279</v>
+        <v>299</v>
       </c>
     </row>
     <row r="94">
@@ -11488,7 +11488,7 @@
         <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>477</v>
+        <v>488</v>
       </c>
     </row>
     <row r="94">
@@ -15013,7 +15013,7 @@
         <v>140659</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
@@ -18525,7 +18525,7 @@
         <v>79204</v>
       </c>
       <c r="K93" t="n">
-        <v>438</v>
+        <v>449</v>
       </c>
     </row>
     <row r="94">
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189606</v>
       </c>
       <c r="K93" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="94">
@@ -25549,7 +25549,7 @@
         <v>61366</v>
       </c>
       <c r="K93" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94">
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>355</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94">
@@ -32555,7 +32555,7 @@
         <v>0.002501341800186784</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -32573,7 +32573,7 @@
         <v>54810</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94">
@@ -39597,7 +39597,7 @@
         <v>52797</v>
       </c>
       <c r="K93" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69610</v>
       </c>
       <c r="K93" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
     </row>
     <row r="94">
@@ -11488,7 +11488,7 @@
         <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="94">
@@ -15013,7 +15013,7 @@
         <v>140659</v>
       </c>
       <c r="K93" t="n">
-        <v>23</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94">
@@ -18525,7 +18525,7 @@
         <v>79204</v>
       </c>
       <c r="K93" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="94">
@@ -22037,7 +22037,7 @@
         <v>189606</v>
       </c>
       <c r="K93" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94">
@@ -25549,7 +25549,7 @@
         <v>61366</v>
       </c>
       <c r="K93" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94">
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="94">
@@ -32573,7 +32573,7 @@
         <v>54810</v>
       </c>
       <c r="K93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94">
@@ -39597,7 +39597,7 @@
         <v>52797</v>
       </c>
       <c r="K93" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7961,22 +7961,22 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>560812</v>
+        <v>555100</v>
       </c>
       <c r="G93" t="n">
-        <v>5908</v>
+        <v>14163</v>
       </c>
       <c r="H93" t="n">
         <v>37852</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.01737835404589016</v>
+        <v>0.02165773376301021</v>
       </c>
       <c r="J93" t="n">
-        <v>69610</v>
+        <v>69659</v>
       </c>
       <c r="K93" t="n">
-        <v>318</v>
+        <v>277</v>
       </c>
     </row>
     <row r="94">
@@ -7989,16 +7989,16 @@
         <v>135789</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>340151</v>
+        <v>334439</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>5908</v>
+        <v>14163</v>
       </c>
       <c r="H94" s="6" t="n">
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69610</v>
+        <v>69659</v>
       </c>
     </row>
   </sheetData>
@@ -11488,7 +11488,7 @@
         <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>499</v>
+        <v>510</v>
       </c>
     </row>
     <row r="94">
@@ -14995,7 +14995,7 @@
         <v>0.005204784375697741</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>1176979</v>
@@ -15010,10 +15010,10 @@
         <v>0.005765059242268695</v>
       </c>
       <c r="J93" t="n">
-        <v>140659</v>
+        <v>140989</v>
       </c>
       <c r="K93" t="n">
-        <v>306</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -15035,7 +15035,7 @@
         <v>115237</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>140659</v>
+        <v>140989</v>
       </c>
     </row>
   </sheetData>
@@ -18522,10 +18522,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>79204</v>
+        <v>79229</v>
       </c>
       <c r="K93" t="n">
-        <v>451</v>
+        <v>432</v>
       </c>
     </row>
     <row r="94">
@@ -18547,7 +18547,7 @@
         <v>231827</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79204</v>
+        <v>79229</v>
       </c>
     </row>
   </sheetData>
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189606</v>
+        <v>189684</v>
       </c>
       <c r="K93" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94">
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189606</v>
+        <v>189684</v>
       </c>
     </row>
   </sheetData>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61366</v>
+        <v>61405</v>
       </c>
       <c r="K93" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61366</v>
+        <v>61405</v>
       </c>
     </row>
   </sheetData>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94">
@@ -32570,10 +32570,10 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54810</v>
+        <v>54589</v>
       </c>
       <c r="K93" t="n">
-        <v>6</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94">
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54810</v>
+        <v>54589</v>
       </c>
     </row>
   </sheetData>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="94">
@@ -39579,7 +39579,7 @@
         <v>0.006207474992943777</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>295759</v>
@@ -39594,7 +39594,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>52797</v>
+        <v>52799</v>
       </c>
       <c r="K93" t="n">
         <v>82</v>
@@ -39619,7 +39619,7 @@
         <v>72</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>52797</v>
+        <v>52799</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69659</v>
       </c>
       <c r="K93" t="n">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="94">
@@ -11488,7 +11488,7 @@
         <v>79441</v>
       </c>
       <c r="K93" t="n">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="94">
@@ -14995,7 +14995,7 @@
         <v>0.005204784375697741</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>1176979</v>
@@ -15010,10 +15010,10 @@
         <v>0.005765059242268695</v>
       </c>
       <c r="J93" t="n">
-        <v>140989</v>
+        <v>141005</v>
       </c>
       <c r="K93" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -15035,7 +15035,7 @@
         <v>115237</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>140989</v>
+        <v>141005</v>
       </c>
     </row>
   </sheetData>
@@ -18522,10 +18522,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>79229</v>
+        <v>79314</v>
       </c>
       <c r="K93" t="n">
-        <v>432</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94">
@@ -18547,7 +18547,7 @@
         <v>231827</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79229</v>
+        <v>79314</v>
       </c>
     </row>
   </sheetData>
@@ -19503,7 +19503,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189684</v>
       </c>
       <c r="K93" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94">
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61405</v>
+        <v>56248</v>
       </c>
       <c r="K93" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61405</v>
+        <v>56248</v>
       </c>
     </row>
   </sheetData>
@@ -29034,13 +29034,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>935351</v>
+        <v>935927</v>
       </c>
       <c r="C93" t="n">
         <v>11614</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>0.0006082590169647241</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="94">
@@ -29071,7 +29071,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>92870</v>
+        <v>93446</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>224466</v>
@@ -32570,10 +32570,10 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54589</v>
+        <v>54816</v>
       </c>
       <c r="K93" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54589</v>
+        <v>54816</v>
       </c>
     </row>
   </sheetData>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94">
@@ -39597,7 +39597,7 @@
         <v>52799</v>
       </c>
       <c r="K93" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>555100</v>
+        <v>559317</v>
       </c>
       <c r="G93" t="n">
         <v>14163</v>
@@ -7970,13 +7970,13 @@
         <v>37852</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.02165773376301021</v>
+        <v>0.02875413339615815</v>
       </c>
       <c r="J93" t="n">
-        <v>69659</v>
+        <v>69672</v>
       </c>
       <c r="K93" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="94">
@@ -7989,7 +7989,7 @@
         <v>135789</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>334439</v>
+        <v>338656</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>14163</v>
@@ -7998,7 +7998,7 @@
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69659</v>
+        <v>69672</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11485,10 +11485,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>79441</v>
+        <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>518</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94">
@@ -11510,7 +11510,7 @@
         <v>94589</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79441</v>
+        <v>79768</v>
       </c>
     </row>
   </sheetData>
@@ -14986,16 +14986,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1737792</v>
+        <v>1737928</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.005204784375697741</v>
+        <v>0.005283451932387549</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>1176979</v>
@@ -15010,10 +15010,10 @@
         <v>0.005765059242268695</v>
       </c>
       <c r="J93" t="n">
-        <v>141005</v>
+        <v>141014</v>
       </c>
       <c r="K93" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>530441</v>
+        <v>530577</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>634383</v>
@@ -15035,7 +15035,7 @@
         <v>115237</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>141005</v>
+        <v>141014</v>
       </c>
     </row>
   </sheetData>
@@ -18507,7 +18507,7 @@
         <v>-0.000437165820358476</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>534752</v>
@@ -18525,7 +18525,7 @@
         <v>79314</v>
       </c>
       <c r="K93" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94">
@@ -19503,7 +19503,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189684</v>
+        <v>189753</v>
       </c>
       <c r="K93" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94">
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189684</v>
+        <v>189753</v>
       </c>
     </row>
   </sheetData>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56248</v>
+        <v>61404</v>
       </c>
       <c r="K93" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56248</v>
+        <v>61404</v>
       </c>
     </row>
   </sheetData>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94">
@@ -32546,16 +32546,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>797563</v>
+        <v>797662</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.002501341800186784</v>
+        <v>0.00262578041235688</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -32570,7 +32570,7 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54816</v>
+        <v>54817</v>
       </c>
       <c r="K93" t="n">
         <v>3</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>103727</v>
+        <v>103826</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>194866</v>
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54816</v>
+        <v>54817</v>
       </c>
     </row>
   </sheetData>
@@ -36067,7 +36067,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>358699</v>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94">
@@ -39597,7 +39597,7 @@
         <v>52799</v>
       </c>
       <c r="K93" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7958,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>559317</v>
@@ -7973,7 +7973,7 @@
         <v>0.02875413339615815</v>
       </c>
       <c r="J93" t="n">
-        <v>69672</v>
+        <v>69685</v>
       </c>
       <c r="K93" t="n">
         <v>293</v>
@@ -7998,7 +7998,7 @@
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69672</v>
+        <v>69685</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
     </row>
     <row r="94">
@@ -14986,16 +14986,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1737928</v>
+        <v>1738139</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.005283451932387549</v>
+        <v>0.005405502332840119</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>1176979</v>
@@ -15013,7 +15013,7 @@
         <v>141014</v>
       </c>
       <c r="K93" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>530577</v>
+        <v>530788</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>634383</v>
@@ -18522,10 +18522,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>79314</v>
+        <v>79450</v>
       </c>
       <c r="K93" t="n">
-        <v>356</v>
+        <v>235</v>
       </c>
     </row>
     <row r="94">
@@ -18547,7 +18547,7 @@
         <v>231827</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79314</v>
+        <v>79450</v>
       </c>
     </row>
   </sheetData>
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189753</v>
       </c>
       <c r="K93" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94">
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61404</v>
+        <v>61436</v>
       </c>
       <c r="K93" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61404</v>
+        <v>61436</v>
       </c>
     </row>
   </sheetData>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="94">
@@ -32570,10 +32570,10 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54817</v>
+        <v>54789</v>
       </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94">
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54817</v>
+        <v>54789</v>
       </c>
     </row>
   </sheetData>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94">
@@ -39594,7 +39594,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>52799</v>
+        <v>52802</v>
       </c>
       <c r="K93" t="n">
         <v>89</v>
@@ -39619,7 +39619,7 @@
         <v>72</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>52799</v>
+        <v>52802</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69685</v>
       </c>
       <c r="K93" t="n">
-        <v>293</v>
+        <v>321</v>
       </c>
     </row>
     <row r="94">
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>216</v>
+        <v>260</v>
       </c>
     </row>
     <row r="94">
@@ -14986,34 +14986,34 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1738139</v>
+        <v>1743332</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.005405502332840119</v>
+        <v>0.008409330434973744</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>1176979</v>
+        <v>1177927</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>115237</v>
+        <v>115263</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.005765059242268695</v>
+        <v>0.006523148576948013</v>
       </c>
       <c r="J93" t="n">
-        <v>141014</v>
+        <v>141087</v>
       </c>
       <c r="K93" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94">
@@ -15023,19 +15023,19 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>530788</v>
+        <v>535981</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>634383</v>
+        <v>635331</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>115237</v>
+        <v>115263</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>141014</v>
+        <v>141087</v>
       </c>
     </row>
   </sheetData>
@@ -18498,16 +18498,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1218684</v>
+        <v>1219152</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>-0.000437165820358476</v>
+        <v>-5.331290492176536e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>534752</v>
@@ -18525,7 +18525,7 @@
         <v>79450</v>
       </c>
       <c r="K93" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>88621</v>
+        <v>89089</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>299895</v>
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189753</v>
       </c>
       <c r="K93" t="n">
-        <v>79</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94">
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61436</v>
+        <v>61441</v>
       </c>
       <c r="K93" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61436</v>
+        <v>61441</v>
       </c>
     </row>
   </sheetData>
@@ -29034,13 +29034,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>935927</v>
+        <v>937682</v>
       </c>
       <c r="C93" t="n">
         <v>11614</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.0006082590169647241</v>
+        <v>0.002461548209279118</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>418</v>
+        <v>444</v>
       </c>
     </row>
     <row r="94">
@@ -29071,7 +29071,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>93446</v>
+        <v>95201</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>224466</v>
@@ -32546,13 +32546,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>797662</v>
+        <v>797729</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.00262578041235688</v>
+        <v>0.00270999644281543</v>
       </c>
       <c r="E93" t="n">
         <v>4</v>
@@ -32570,10 +32570,10 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54789</v>
+        <v>54834</v>
       </c>
       <c r="K93" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>103826</v>
+        <v>103893</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>194866</v>
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54789</v>
+        <v>54834</v>
       </c>
     </row>
   </sheetData>
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94">
@@ -39594,10 +39594,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>52802</v>
+        <v>52805</v>
       </c>
       <c r="K93" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94">
@@ -39619,7 +39619,7 @@
         <v>72</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>52802</v>
+        <v>52805</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69685</v>
       </c>
       <c r="K93" t="n">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94">
@@ -11488,7 +11488,7 @@
         <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>260</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94">
@@ -15013,7 +15013,7 @@
         <v>141087</v>
       </c>
       <c r="K93" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94">
@@ -18525,7 +18525,7 @@
         <v>79450</v>
       </c>
       <c r="K93" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94">
@@ -22037,7 +22037,7 @@
         <v>189753</v>
       </c>
       <c r="K93" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94">
@@ -25549,7 +25549,7 @@
         <v>61441</v>
       </c>
       <c r="K93" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94">
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="94">
@@ -32573,7 +32573,7 @@
         <v>54834</v>
       </c>
       <c r="K93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -36085,7 +36085,7 @@
         <v>56436</v>
       </c>
       <c r="K93" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94">
@@ -39597,7 +39597,7 @@
         <v>52805</v>
       </c>
       <c r="K93" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69685</v>
       </c>
       <c r="K93" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94">
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>302</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94">
@@ -15010,10 +15010,10 @@
         <v>0.006523148576948013</v>
       </c>
       <c r="J93" t="n">
-        <v>141087</v>
+        <v>141152</v>
       </c>
       <c r="K93" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -15035,7 +15035,7 @@
         <v>115263</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>141087</v>
+        <v>141152</v>
       </c>
     </row>
   </sheetData>
@@ -18507,7 +18507,7 @@
         <v>-5.331290492176536e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>534752</v>
@@ -18525,7 +18525,7 @@
         <v>79450</v>
       </c>
       <c r="K93" t="n">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94">
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189753</v>
+        <v>189854</v>
       </c>
       <c r="K93" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94">
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189753</v>
+        <v>189854</v>
       </c>
     </row>
   </sheetData>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61441</v>
+        <v>61509</v>
       </c>
       <c r="K93" t="n">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61441</v>
+        <v>61509</v>
       </c>
     </row>
   </sheetData>
@@ -29034,34 +29034,34 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>937682</v>
+        <v>938820</v>
       </c>
       <c r="C93" t="n">
         <v>11614</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.002461548209279118</v>
+        <v>0.003663282169879563</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>499378</v>
+        <v>510569</v>
       </c>
       <c r="G93" t="n">
         <v>6655</v>
       </c>
       <c r="H93" t="n">
-        <v>102317</v>
+        <v>128398</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0</v>
+        <v>0.06126736253801265</v>
       </c>
       <c r="J93" t="n">
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94">
@@ -29071,16 +29071,16 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>95201</v>
+        <v>96339</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>224466</v>
+        <v>235657</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>6655</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>102317</v>
+        <v>128398</v>
       </c>
       <c r="J94" s="6" t="n">
         <v>66062</v>
@@ -32570,10 +32570,10 @@
         <v>0.01017009396157837</v>
       </c>
       <c r="J93" t="n">
-        <v>54834</v>
+        <v>54845</v>
       </c>
       <c r="K93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -32595,7 +32595,7 @@
         <v>51058</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>54834</v>
+        <v>54845</v>
       </c>
     </row>
   </sheetData>
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56436</v>
+        <v>56432</v>
       </c>
       <c r="K93" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56436</v>
+        <v>56432</v>
       </c>
     </row>
   </sheetData>
@@ -39597,7 +39597,7 @@
         <v>52805</v>
       </c>
       <c r="K93" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7973,10 +7973,10 @@
         <v>0.02875413339615815</v>
       </c>
       <c r="J93" t="n">
-        <v>69685</v>
+        <v>69723</v>
       </c>
       <c r="K93" t="n">
-        <v>359</v>
+        <v>329</v>
       </c>
     </row>
     <row r="94">
@@ -7998,7 +7998,7 @@
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69685</v>
+        <v>69723</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="94">
@@ -14998,22 +14998,22 @@
         <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>1177927</v>
+        <v>1178623</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>115263</v>
+        <v>115278</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.006523148576948013</v>
+        <v>0.007076538224747803</v>
       </c>
       <c r="J93" t="n">
         <v>141152</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
@@ -15026,13 +15026,13 @@
         <v>535981</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>635331</v>
+        <v>636027</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>115263</v>
+        <v>115278</v>
       </c>
       <c r="J94" s="6" t="n">
         <v>141152</v>
@@ -18498,16 +18498,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1219152</v>
+        <v>1219145</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>-5.331290492176536e-05</v>
+        <v>-5.905429468257086e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>534752</v>
@@ -18525,7 +18525,7 @@
         <v>79450</v>
       </c>
       <c r="K93" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="94">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>89089</v>
+        <v>89082</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>299895</v>
@@ -22019,7 +22019,7 @@
         <v>0.0003920517277661988</v>
       </c>
       <c r="E93" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189854</v>
       </c>
       <c r="K93" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94">
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61509</v>
+        <v>61570</v>
       </c>
       <c r="K93" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61509</v>
+        <v>61570</v>
       </c>
     </row>
   </sheetData>
@@ -29061,7 +29061,7 @@
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>458</v>
+        <v>474</v>
       </c>
     </row>
     <row r="94">
@@ -32573,7 +32573,7 @@
         <v>54845</v>
       </c>
       <c r="K93" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56432</v>
+        <v>56524</v>
       </c>
       <c r="K93" t="n">
-        <v>211</v>
+        <v>135</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56432</v>
+        <v>56524</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7973,10 +7973,10 @@
         <v>0.02875413339615815</v>
       </c>
       <c r="J93" t="n">
-        <v>69723</v>
+        <v>69788</v>
       </c>
       <c r="K93" t="n">
-        <v>329</v>
+        <v>274</v>
       </c>
     </row>
     <row r="94">
@@ -7998,7 +7998,7 @@
         <v>37852</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>69723</v>
+        <v>69788</v>
       </c>
     </row>
   </sheetData>
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
     </row>
     <row r="94">
@@ -14995,7 +14995,7 @@
         <v>0.008409330434973744</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
         <v>1178623</v>
@@ -15010,10 +15010,10 @@
         <v>0.007076538224747803</v>
       </c>
       <c r="J93" t="n">
-        <v>141152</v>
+        <v>141168</v>
       </c>
       <c r="K93" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -15035,7 +15035,7 @@
         <v>115278</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>141152</v>
+        <v>141168</v>
       </c>
     </row>
   </sheetData>
@@ -18525,7 +18525,7 @@
         <v>79450</v>
       </c>
       <c r="K93" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94">
@@ -22010,16 +22010,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3072569</v>
+        <v>3072616</v>
       </c>
       <c r="C93" t="n">
         <v>50692</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.0003920517277661988</v>
+        <v>0.0004071060016265022</v>
       </c>
       <c r="E93" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189854</v>
+        <v>189861</v>
       </c>
       <c r="K93" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94">
@@ -22047,7 +22047,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>736748</v>
+        <v>736795</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>958303</v>
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189854</v>
+        <v>189861</v>
       </c>
     </row>
   </sheetData>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61570</v>
+        <v>61612</v>
       </c>
       <c r="K93" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61570</v>
+        <v>61612</v>
       </c>
     </row>
   </sheetData>
@@ -29046,7 +29046,7 @@
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>510569</v>
+        <v>511219</v>
       </c>
       <c r="G93" t="n">
         <v>6655</v>
@@ -29055,13 +29055,13 @@
         <v>128398</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.06126736253801265</v>
+        <v>0.06233582641571464</v>
       </c>
       <c r="J93" t="n">
         <v>66062</v>
       </c>
       <c r="K93" t="n">
-        <v>474</v>
+        <v>492</v>
       </c>
     </row>
     <row r="94">
@@ -29074,7 +29074,7 @@
         <v>96339</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>235657</v>
+        <v>236307</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>6655</v>
@@ -32573,7 +32573,7 @@
         <v>54845</v>
       </c>
       <c r="K93" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56524</v>
+        <v>56578</v>
       </c>
       <c r="K93" t="n">
-        <v>135</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56524</v>
+        <v>56578</v>
       </c>
     </row>
   </sheetData>
@@ -39579,7 +39579,7 @@
         <v>0.006207474992943777</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F93" t="n">
         <v>295759</v>
@@ -39594,10 +39594,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>52805</v>
+        <v>52807</v>
       </c>
       <c r="K93" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="94">
@@ -39619,7 +39619,7 @@
         <v>72</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>52805</v>
+        <v>52807</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69788</v>
       </c>
       <c r="K93" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94">
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11488,7 +11488,7 @@
         <v>79768</v>
       </c>
       <c r="K93" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="94">
@@ -14986,16 +14986,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1743332</v>
+        <v>1743730</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.008409330434973744</v>
+        <v>0.0086395487258748</v>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
         <v>1178623</v>
@@ -15013,7 +15013,7 @@
         <v>141168</v>
       </c>
       <c r="K93" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>535981</v>
+        <v>536379</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>636027</v>
@@ -18498,34 +18498,34 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1219145</v>
+        <v>1219232</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>-5.905429468257086e-05</v>
+        <v>1.230297805886893e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
-        <v>534752</v>
+        <v>535369</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>231827</v>
+        <v>246998</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0</v>
+        <v>0.02059539851730872</v>
       </c>
       <c r="J93" t="n">
-        <v>79450</v>
+        <v>79559</v>
       </c>
       <c r="K93" t="n">
-        <v>280</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94">
@@ -18535,19 +18535,19 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>89082</v>
+        <v>89169</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>299895</v>
+        <v>300512</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>231827</v>
+        <v>246998</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79450</v>
+        <v>79559</v>
       </c>
     </row>
   </sheetData>
@@ -22010,16 +22010,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3072616</v>
+        <v>3072838</v>
       </c>
       <c r="C93" t="n">
         <v>50692</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.0004071060016265022</v>
+        <v>0.000478213422838999</v>
       </c>
       <c r="E93" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22037,7 +22037,7 @@
         <v>189861</v>
       </c>
       <c r="K93" t="n">
-        <v>149</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94">
@@ -22047,7 +22047,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>736795</v>
+        <v>737017</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>958303</v>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61612</v>
+        <v>61628</v>
       </c>
       <c r="K93" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61612</v>
+        <v>61628</v>
       </c>
     </row>
   </sheetData>
@@ -29034,13 +29034,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>938820</v>
+        <v>939673</v>
       </c>
       <c r="C93" t="n">
         <v>11614</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.003663282169879563</v>
+        <v>0.004564054637711003</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -29058,10 +29058,10 @@
         <v>0.06233582641571464</v>
       </c>
       <c r="J93" t="n">
-        <v>66062</v>
+        <v>66061</v>
       </c>
       <c r="K93" t="n">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="94">
@@ -29071,7 +29071,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>96339</v>
+        <v>97192</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>236307</v>
@@ -29083,7 +29083,7 @@
         <v>128398</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>66062</v>
+        <v>66061</v>
       </c>
     </row>
   </sheetData>
@@ -32555,7 +32555,7 @@
         <v>0.00270999644281543</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -32573,7 +32573,7 @@
         <v>54845</v>
       </c>
       <c r="K93" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56578</v>
+        <v>56630</v>
       </c>
       <c r="K93" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56578</v>
+        <v>56630</v>
       </c>
     </row>
   </sheetData>
@@ -39597,7 +39597,7 @@
         <v>52807</v>
       </c>
       <c r="K93" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7976,7 +7976,7 @@
         <v>69788</v>
       </c>
       <c r="K93" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94">
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -14986,16 +14986,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1743730</v>
+        <v>1744785</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.0086395487258748</v>
+        <v>0.00924980072813765</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F93" t="n">
         <v>1178623</v>
@@ -15010,10 +15010,10 @@
         <v>0.007076538224747803</v>
       </c>
       <c r="J93" t="n">
-        <v>141168</v>
+        <v>141190</v>
       </c>
       <c r="K93" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>536379</v>
+        <v>537434</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>636027</v>
@@ -15035,7 +15035,7 @@
         <v>115278</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>141168</v>
+        <v>141190</v>
       </c>
     </row>
   </sheetData>
@@ -18507,7 +18507,7 @@
         <v>1.230297805886893e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
         <v>535369</v>
@@ -18522,10 +18522,10 @@
         <v>0.02059539851730872</v>
       </c>
       <c r="J93" t="n">
-        <v>79559</v>
+        <v>79598</v>
       </c>
       <c r="K93" t="n">
-        <v>178</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94">
@@ -18547,7 +18547,7 @@
         <v>246998</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79559</v>
+        <v>79598</v>
       </c>
     </row>
   </sheetData>
@@ -22019,7 +22019,7 @@
         <v>0.000478213422838999</v>
       </c>
       <c r="E93" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189861</v>
+        <v>189946</v>
       </c>
       <c r="K93" t="n">
-        <v>178</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94">
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189861</v>
+        <v>189946</v>
       </c>
     </row>
   </sheetData>
@@ -25546,10 +25546,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61628</v>
+        <v>61656</v>
       </c>
       <c r="K93" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94">
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61628</v>
+        <v>61656</v>
       </c>
     </row>
   </sheetData>
@@ -29043,7 +29043,7 @@
         <v>0.004564054637711003</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>511219</v>
@@ -32573,7 +32573,7 @@
         <v>54845</v>
       </c>
       <c r="K93" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94">
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56630</v>
+        <v>56608</v>
       </c>
       <c r="K93" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56630</v>
+        <v>56608</v>
       </c>
     </row>
   </sheetData>
@@ -39579,7 +39579,7 @@
         <v>0.006207474992943777</v>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -22019,7 +22019,7 @@
         <v>0.000478213422838999</v>
       </c>
       <c r="E93" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -22019,7 +22019,7 @@
         <v>0.000478213422838999</v>
       </c>
       <c r="E93" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7958,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>559317</v>
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -14995,19 +14995,19 @@
         <v>0.00924980072813765</v>
       </c>
       <c r="E93" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F93" t="n">
-        <v>1178623</v>
+        <v>1179778</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>115278</v>
+        <v>115284</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.007076538224747803</v>
+        <v>0.007980174485079105</v>
       </c>
       <c r="J93" t="n">
         <v>141190</v>
@@ -15026,13 +15026,13 @@
         <v>537434</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>636027</v>
+        <v>637182</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>115278</v>
+        <v>115284</v>
       </c>
       <c r="J94" s="6" t="n">
         <v>141190</v>
@@ -18498,13 +18498,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1219232</v>
+        <v>1219230</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1.230297805886893e-05</v>
+        <v>1.066258098435307e-05</v>
       </c>
       <c r="E93" t="n">
         <v>11</v>
@@ -18522,10 +18522,10 @@
         <v>0.02059539851730872</v>
       </c>
       <c r="J93" t="n">
-        <v>79598</v>
+        <v>79735</v>
       </c>
       <c r="K93" t="n">
-        <v>139</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>89169</v>
+        <v>89167</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>300512</v>
@@ -18547,7 +18547,7 @@
         <v>246998</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79598</v>
+        <v>79735</v>
       </c>
     </row>
   </sheetData>
@@ -22019,7 +22019,7 @@
         <v>0.000478213422838999</v>
       </c>
       <c r="E93" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,10 +22034,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>189946</v>
+        <v>190046</v>
       </c>
       <c r="K93" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>189946</v>
+        <v>190046</v>
       </c>
     </row>
   </sheetData>
@@ -25522,13 +25522,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>956245</v>
+        <v>948503</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>-0.008096251483667889</v>
       </c>
       <c r="E93" t="n">
         <v>9</v>
@@ -25549,7 +25549,7 @@
         <v>61656</v>
       </c>
       <c r="K93" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -25559,7 +25559,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>227355</v>
+        <v>219613</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>358194</v>
@@ -29034,13 +29034,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>939673</v>
+        <v>939700</v>
       </c>
       <c r="C93" t="n">
         <v>11614</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0.004564054637711003</v>
+        <v>0.004592566779131224</v>
       </c>
       <c r="E93" t="n">
         <v>3</v>
@@ -29071,7 +29071,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>97192</v>
+        <v>97219</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>236307</v>
@@ -32555,7 +32555,7 @@
         <v>0.00270999644281543</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -34994,7 +34994,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>283177</v>
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="K93" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -11470,7 +11470,7 @@
         <v>0.006590338257587016</v>
       </c>
       <c r="E93" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F93" t="n">
         <v>750284</v>
@@ -11485,10 +11485,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>79768</v>
+        <v>79818</v>
       </c>
       <c r="K93" t="n">
-        <v>345</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94">
@@ -11510,7 +11510,7 @@
         <v>94589</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>79768</v>
+        <v>79818</v>
       </c>
     </row>
   </sheetData>
@@ -14995,7 +14995,7 @@
         <v>0.00924980072813765</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
         <v>1179778</v>
@@ -15004,10 +15004,10 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>115284</v>
+        <v>134808</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.007980174485079105</v>
+        <v>0.02317620751411299</v>
       </c>
       <c r="J93" t="n">
         <v>141190</v>
@@ -15032,7 +15032,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>115284</v>
+        <v>134808</v>
       </c>
       <c r="J94" s="6" t="n">
         <v>141190</v>
@@ -18498,16 +18498,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1219230</v>
+        <v>1219332</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1.066258098435307e-05</v>
+        <v>9.43228317846618e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F93" t="n">
         <v>535369</v>
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>89167</v>
+        <v>89269</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>300512</v>
@@ -22019,7 +22019,7 @@
         <v>0.000478213422838999</v>
       </c>
       <c r="E93" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22034,7 +22034,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>190046</v>
+        <v>190045</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -22059,7 +22059,7 @@
         <v>154953</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>190046</v>
+        <v>190045</v>
       </c>
     </row>
   </sheetData>
@@ -25531,7 +25531,7 @@
         <v>-0.008096251483667889</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25546,7 +25546,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>61656</v>
+        <v>61655</v>
       </c>
       <c r="K93" t="n">
         <v>96</v>
@@ -25571,7 +25571,7 @@
         <v>80609</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>61656</v>
+        <v>61655</v>
       </c>
     </row>
   </sheetData>
@@ -32555,7 +32555,7 @@
         <v>0.00270999644281543</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -36067,7 +36067,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>358699</v>
@@ -36082,10 +36082,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>56610</v>
+        <v>56569</v>
       </c>
       <c r="K93" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94">
@@ -36107,7 +36107,7 @@
         <v>28881</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>56610</v>
+        <v>56569</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$93</f>
+              <f>'PNB'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$B$2:$B$93</f>
+              <f>'PNB'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -224,12 +224,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$93</f>
+              <f>'PNB'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$F$2:$F$93</f>
+              <f>'PNB'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -255,12 +255,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$93</f>
+              <f>'PNB'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$G$2:$G$93</f>
+              <f>'PNB'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -286,12 +286,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$93</f>
+              <f>'PNB'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$H$2:$H$93</f>
+              <f>'PNB'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -371,12 +371,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$93</f>
+              <f>'JIM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$J$2:$J$93</f>
+              <f>'JIM'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$93</f>
+              <f>'JIM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$K$2:$K$93</f>
+              <f>'JIM'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -486,12 +486,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$93</f>
+              <f>'NDI'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$B$2:$B$93</f>
+              <f>'NDI'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -516,12 +516,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$93</f>
+              <f>'NDI'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$F$2:$F$93</f>
+              <f>'NDI'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -547,12 +547,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$93</f>
+              <f>'NDI'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$G$2:$G$93</f>
+              <f>'NDI'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -578,12 +578,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$93</f>
+              <f>'NDI'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$H$2:$H$93</f>
+              <f>'NDI'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -663,12 +663,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$93</f>
+              <f>'NDI'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$J$2:$J$93</f>
+              <f>'NDI'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -693,12 +693,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$93</f>
+              <f>'NDI'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$K$2:$K$93</f>
+              <f>'NDI'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -778,12 +778,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$93</f>
+              <f>'CXM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$B$2:$B$93</f>
+              <f>'CXM'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -808,12 +808,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$93</f>
+              <f>'CXM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$F$2:$F$93</f>
+              <f>'CXM'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -839,12 +839,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$93</f>
+              <f>'CXM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$G$2:$G$93</f>
+              <f>'CXM'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -870,12 +870,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$93</f>
+              <f>'CXM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$H$2:$H$93</f>
+              <f>'CXM'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -955,12 +955,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$93</f>
+              <f>'CXM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$J$2:$J$93</f>
+              <f>'CXM'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -985,12 +985,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$93</f>
+              <f>'CXM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$K$2:$K$93</f>
+              <f>'CXM'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1070,12 +1070,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$93</f>
+              <f>'AUA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$B$2:$B$93</f>
+              <f>'AUA'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1100,12 +1100,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$93</f>
+              <f>'AUA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$F$2:$F$93</f>
+              <f>'AUA'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$93</f>
+              <f>'AUA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$G$2:$G$93</f>
+              <f>'AUA'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1162,12 +1162,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$93</f>
+              <f>'AUA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$H$2:$H$93</f>
+              <f>'AUA'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1247,12 +1247,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$93</f>
+              <f>'AUA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$J$2:$J$93</f>
+              <f>'AUA'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1277,12 +1277,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$93</f>
+              <f>'AUA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$K$2:$K$93</f>
+              <f>'AUA'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1362,12 +1362,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$93</f>
+              <f>'CMA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$B$2:$B$93</f>
+              <f>'CMA'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1392,12 +1392,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$93</f>
+              <f>'CMA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$F$2:$F$93</f>
+              <f>'CMA'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$93</f>
+              <f>'CMA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$G$2:$G$93</f>
+              <f>'CMA'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1454,12 +1454,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$93</f>
+              <f>'CMA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$H$2:$H$93</f>
+              <f>'CMA'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1539,12 +1539,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$93</f>
+              <f>'CMA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$J$2:$J$93</f>
+              <f>'CMA'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1569,12 +1569,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$93</f>
+              <f>'CMA'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$K$2:$K$93</f>
+              <f>'CMA'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1654,12 +1654,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$93</f>
+              <f>'PPR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$B$2:$B$93</f>
+              <f>'PPR'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1684,12 +1684,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$93</f>
+              <f>'PPR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$F$2:$F$93</f>
+              <f>'PPR'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1715,12 +1715,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$93</f>
+              <f>'PPR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$G$2:$G$93</f>
+              <f>'PPR'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1746,12 +1746,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$93</f>
+              <f>'PPR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$H$2:$H$93</f>
+              <f>'PPR'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1831,12 +1831,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$93</f>
+              <f>'PNB'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$J$2:$J$93</f>
+              <f>'PNB'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1861,12 +1861,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$93</f>
+              <f>'PNB'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$K$2:$K$93</f>
+              <f>'PNB'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1946,12 +1946,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$93</f>
+              <f>'PPR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$J$2:$J$93</f>
+              <f>'PPR'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -1976,12 +1976,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$93</f>
+              <f>'PPR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$K$2:$K$93</f>
+              <f>'PPR'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2061,12 +2061,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$93</f>
+              <f>'TLS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$B$2:$B$93</f>
+              <f>'TLS'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2091,12 +2091,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$93</f>
+              <f>'TLS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$F$2:$F$93</f>
+              <f>'TLS'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2122,12 +2122,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$93</f>
+              <f>'TLS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$G$2:$G$93</f>
+              <f>'TLS'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$93</f>
+              <f>'TLS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$H$2:$H$93</f>
+              <f>'TLS'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2238,12 +2238,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$93</f>
+              <f>'TLS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$J$2:$J$93</f>
+              <f>'TLS'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2268,12 +2268,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$93</f>
+              <f>'TLS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$K$2:$K$93</f>
+              <f>'TLS'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2353,12 +2353,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$93</f>
+              <f>'NVR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$B$2:$B$93</f>
+              <f>'NVR'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2383,12 +2383,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$93</f>
+              <f>'NVR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$F$2:$F$93</f>
+              <f>'NVR'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2414,12 +2414,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$93</f>
+              <f>'NVR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$G$2:$G$93</f>
+              <f>'NVR'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2445,12 +2445,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$93</f>
+              <f>'NVR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$H$2:$H$93</f>
+              <f>'NVR'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2530,12 +2530,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$93</f>
+              <f>'NVR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$J$2:$J$93</f>
+              <f>'NVR'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2560,12 +2560,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$93</f>
+              <f>'NVR'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$K$2:$K$93</f>
+              <f>'NVR'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2645,12 +2645,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$93</f>
+              <f>'DOS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$B$2:$B$93</f>
+              <f>'DOS'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2675,12 +2675,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$93</f>
+              <f>'DOS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$F$2:$F$93</f>
+              <f>'DOS'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2706,12 +2706,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$93</f>
+              <f>'DOS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$G$2:$G$93</f>
+              <f>'DOS'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2737,12 +2737,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$93</f>
+              <f>'DOS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$H$2:$H$93</f>
+              <f>'DOS'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2822,12 +2822,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$93</f>
+              <f>'DOS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$J$2:$J$93</f>
+              <f>'DOS'!$J$2:$J$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2852,12 +2852,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$93</f>
+              <f>'DOS'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$K$2:$K$93</f>
+              <f>'DOS'!$K$2:$K$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2937,12 +2937,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$93</f>
+              <f>'JIM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$B$2:$B$93</f>
+              <f>'JIM'!$B$2:$B$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2967,12 +2967,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$93</f>
+              <f>'JIM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$F$2:$F$93</f>
+              <f>'JIM'!$F$2:$F$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -2998,12 +2998,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$93</f>
+              <f>'JIM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$G$2:$G$93</f>
+              <f>'JIM'!$G$2:$G$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -3029,12 +3029,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$93</f>
+              <f>'JIM'!$A$2:$A$94</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$H$2:$H$93</f>
+              <f>'JIM'!$H$2:$H$94</f>
             </numRef>
           </yVal>
         </ser>
@@ -4502,7 +4502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7958,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>559317</v>
@@ -7980,25 +7980,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>757546</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>559561</v>
+      </c>
+      <c r="G94" t="n">
+        <v>14163</v>
+      </c>
+      <c r="H94" t="n">
+        <v>37852</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0.0003991284604764678</v>
+      </c>
+      <c r="J94" t="n">
+        <v>69791</v>
+      </c>
+      <c r="K94" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>135789</v>
       </c>
-      <c r="F94" s="6" t="n">
-        <v>338656</v>
-      </c>
-      <c r="G94" s="6" t="n">
+      <c r="F95" s="6" t="n">
+        <v>338900</v>
+      </c>
+      <c r="G95" s="6" t="n">
         <v>14163</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>37852</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>69788</v>
+      <c r="J95" s="6" t="n">
+        <v>69791</v>
       </c>
     </row>
   </sheetData>
@@ -8014,7 +8051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11492,25 +11529,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1077298</v>
+      </c>
+      <c r="C94" t="n">
+        <v>6373</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>750284</v>
+      </c>
+      <c r="G94" t="n">
+        <v>26677</v>
+      </c>
+      <c r="H94" t="n">
+        <v>94589</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>79825</v>
+      </c>
+      <c r="K94" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>227872</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>251377</v>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="G95" s="6" t="n">
         <v>26677</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>94589</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>79818</v>
+      <c r="J95" s="6" t="n">
+        <v>79825</v>
       </c>
     </row>
   </sheetData>
@@ -11539,7 +11613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14995,7 +15069,7 @@
         <v>0.00924980072813765</v>
       </c>
       <c r="E93" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F93" t="n">
         <v>1179778</v>
@@ -15017,25 +15091,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1744785</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1179778</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>134808</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>141191</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>537434</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>637182</v>
       </c>
-      <c r="G94" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="6" t="n">
+      <c r="G95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="6" t="n">
         <v>134808</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>141190</v>
+      <c r="J95" s="6" t="n">
+        <v>141191</v>
       </c>
     </row>
   </sheetData>
@@ -15051,7 +15162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18507,7 +18618,7 @@
         <v>9.43228317846618e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
         <v>535369</v>
@@ -18529,24 +18640,61 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1219332</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>535369</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>246998</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>79735</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>89269</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>300512</v>
       </c>
-      <c r="G94" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="6" t="n">
+      <c r="G95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="6" t="n">
         <v>246998</v>
       </c>
-      <c r="J94" s="6" t="n">
+      <c r="J95" s="6" t="n">
         <v>79735</v>
       </c>
     </row>
@@ -18563,7 +18711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -22019,7 +22167,7 @@
         <v>0.000478213422838999</v>
       </c>
       <c r="E93" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F93" t="n">
         <v>1842767</v>
@@ -22041,25 +22189,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3072838</v>
+      </c>
+      <c r="C94" t="n">
+        <v>50692</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1842767</v>
+      </c>
+      <c r="G94" t="n">
+        <v>123505</v>
+      </c>
+      <c r="H94" t="n">
+        <v>154953</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>190031</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>737017</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>958303</v>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="G95" s="6" t="n">
         <v>123505</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>154953</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>190045</v>
+      <c r="J95" s="6" t="n">
+        <v>190031</v>
       </c>
     </row>
   </sheetData>
@@ -22075,7 +22260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25531,7 +25716,7 @@
         <v>-0.008096251483667889</v>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
         <v>590365</v>
@@ -25553,25 +25738,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>948503</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>590365</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4948</v>
+      </c>
+      <c r="H94" t="n">
+        <v>80609</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>61652</v>
+      </c>
+      <c r="K94" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>219613</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>358194</v>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="G95" s="6" t="n">
         <v>4948</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>80609</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>61655</v>
+      <c r="J95" s="6" t="n">
+        <v>61652</v>
       </c>
     </row>
   </sheetData>
@@ -25587,7 +25809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -29065,25 +29287,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>939700</v>
+      </c>
+      <c r="C94" t="n">
+        <v>11614</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>511219</v>
+      </c>
+      <c r="G94" t="n">
+        <v>6655</v>
+      </c>
+      <c r="H94" t="n">
+        <v>128398</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>66062</v>
+      </c>
+      <c r="K94" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>97219</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>236307</v>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="G95" s="6" t="n">
         <v>6655</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>128398</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>66061</v>
+      <c r="J95" s="6" t="n">
+        <v>66062</v>
       </c>
     </row>
   </sheetData>
@@ -29099,7 +29358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32555,7 +32814,7 @@
         <v>0.00270999644281543</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
         <v>301273</v>
@@ -32577,25 +32836,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>797729</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>301273</v>
+      </c>
+      <c r="G94" t="n">
+        <v>83</v>
+      </c>
+      <c r="H94" t="n">
+        <v>51058</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>54850</v>
+      </c>
+      <c r="K94" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>103893</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>194866</v>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="G95" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>51058</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>54845</v>
+      <c r="J95" s="6" t="n">
+        <v>54850</v>
       </c>
     </row>
   </sheetData>
@@ -32611,7 +32907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -36089,25 +36385,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>746955</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>358699</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>28881</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>56601</v>
+      </c>
+      <c r="K94" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>256024</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>277278</v>
       </c>
-      <c r="G94" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="6" t="n">
+      <c r="G95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="6" t="n">
         <v>28881</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>56569</v>
+      <c r="J95" s="6" t="n">
+        <v>56601</v>
       </c>
     </row>
   </sheetData>
@@ -36123,7 +36456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39601,25 +39934,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>502660</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>295759</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>72</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>52805</v>
+      </c>
+      <c r="K94" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B95" s="6" t="n">
         <v>-108065</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F95" s="6" t="n">
         <v>-7808</v>
       </c>
-      <c r="G94" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="6" t="n">
+      <c r="G95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="J94" s="6" t="n">
-        <v>52807</v>
+      <c r="J95" s="6" t="n">
+        <v>52805</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7995,25 +7995,25 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>559561</v>
+        <v>559727</v>
       </c>
       <c r="G94" t="n">
         <v>14163</v>
       </c>
       <c r="H94" t="n">
-        <v>37852</v>
+        <v>37774</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.0003991284604764678</v>
+        <v>0.0005430764298286365</v>
       </c>
       <c r="J94" t="n">
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="95">
@@ -8026,13 +8026,13 @@
         <v>135789</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>338900</v>
+        <v>339066</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>14163</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>37852</v>
+        <v>37774</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>69791</v>
@@ -11544,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -11562,7 +11562,7 @@
         <v>79825</v>
       </c>
       <c r="K94" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="95">
@@ -15097,13 +15097,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1744785</v>
+        <v>1747653</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>0.001643755534349504</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -15121,7 +15121,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141191</v>
+        <v>141192</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>537434</v>
+        <v>540302</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>637182</v>
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141191</v>
+        <v>141192</v>
       </c>
     </row>
   </sheetData>
@@ -18670,10 +18670,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>79735</v>
+        <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -18695,7 +18695,7 @@
         <v>246998</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>79735</v>
+        <v>79734</v>
       </c>
     </row>
   </sheetData>
@@ -22204,7 +22204,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22222,7 +22222,7 @@
         <v>190031</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -25753,7 +25753,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>590365</v>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="95">
@@ -32869,7 +32869,7 @@
         <v>54850</v>
       </c>
       <c r="K94" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -36409,10 +36409,10 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>28881</v>
+        <v>28935</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
         <v>56601</v>
@@ -36437,7 +36437,7 @@
         <v>0</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>28881</v>
+        <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>56601</v>
@@ -39967,7 +39967,7 @@
         <v>52805</v>
       </c>
       <c r="K94" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -11544,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -11559,10 +11559,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>79825</v>
+        <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>292</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95">
@@ -11584,7 +11584,7 @@
         <v>94589</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>79825</v>
+        <v>79937</v>
       </c>
     </row>
   </sheetData>
@@ -15097,16 +15097,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1747653</v>
+        <v>1747533</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.001643755534349504</v>
+        <v>0.001574979152159149</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>540302</v>
+        <v>540182</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>637182</v>
@@ -22195,16 +22195,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3072838</v>
+        <v>3073223</v>
       </c>
       <c r="C94" t="n">
         <v>50692</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>737017</v>
+        <v>737402</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>958303</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -25753,7 +25753,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>590365</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>757546</v>
+        <v>759150</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>0.002117363170025319</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>135789</v>
+        <v>137393</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>339066</v>
@@ -11544,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22219,10 +22219,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>190031</v>
+        <v>190055</v>
       </c>
       <c r="K94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -22244,7 +22244,7 @@
         <v>154953</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190031</v>
+        <v>190055</v>
       </c>
     </row>
   </sheetData>
@@ -39940,13 +39940,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>502660</v>
+        <v>503527</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>0.001724823936656985</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -39977,7 +39977,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>-108065</v>
+        <v>-107198</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>-7808</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>759150</v>
+        <v>759602</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.002117363170025319</v>
+        <v>0.002714026606965121</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>137393</v>
+        <v>137845</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>339066</v>
@@ -11544,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -25753,7 +25753,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>590365</v>
@@ -32866,10 +32866,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>54850</v>
+        <v>54862</v>
       </c>
       <c r="K94" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95">
@@ -32891,7 +32891,7 @@
         <v>51058</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54850</v>
+        <v>54862</v>
       </c>
     </row>
   </sheetData>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56601</v>
+        <v>56598</v>
       </c>
       <c r="K94" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56601</v>
+        <v>56598</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>759602</v>
+        <v>759760</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>6421</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.002714026606965121</v>
+        <v>0.01139864773888318</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="95">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>137845</v>
+        <v>138003</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>339066</v>
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95">
@@ -15097,13 +15097,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1747533</v>
+        <v>1748614</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.001574979152159149</v>
+        <v>0.002194539728390604</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -15124,7 +15124,7 @@
         <v>141192</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>540182</v>
+        <v>541263</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>637182</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22219,7 +22219,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>190055</v>
+        <v>190078</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22244,7 +22244,7 @@
         <v>154953</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190055</v>
+        <v>190078</v>
       </c>
     </row>
   </sheetData>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61652</v>
+        <v>61650</v>
       </c>
       <c r="K94" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95">
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61652</v>
+        <v>61650</v>
       </c>
     </row>
   </sheetData>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="95">
@@ -32851,7 +32851,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>301273</v>
@@ -32866,10 +32866,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>54862</v>
+        <v>54878</v>
       </c>
       <c r="K94" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -32891,7 +32891,7 @@
         <v>51058</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54862</v>
+        <v>54878</v>
       </c>
     </row>
   </sheetData>
@@ -36418,7 +36418,7 @@
         <v>56598</v>
       </c>
       <c r="K94" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95">
@@ -39940,13 +39940,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>503527</v>
+        <v>503377</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.001724823936656985</v>
+        <v>0.001426411490868579</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -39967,7 +39967,7 @@
         <v>52805</v>
       </c>
       <c r="K94" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95">
@@ -39977,7 +39977,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>-107198</v>
+        <v>-107348</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>-7808</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -7995,7 +7995,7 @@
         <v>0.01139864773888318</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>559727</v>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="95">
@@ -11544,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95">
@@ -15106,7 +15106,7 @@
         <v>0.002194539728390604</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141192</v>
+        <v>141204</v>
       </c>
       <c r="K94" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141192</v>
+        <v>141204</v>
       </c>
     </row>
   </sheetData>
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>535369</v>
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22219,7 +22219,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>190078</v>
+        <v>190104</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22244,7 +22244,7 @@
         <v>154953</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190078</v>
+        <v>190104</v>
       </c>
     </row>
   </sheetData>
@@ -25771,7 +25771,7 @@
         <v>61650</v>
       </c>
       <c r="K94" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>511219</v>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="95">
@@ -32842,13 +32842,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>797729</v>
+        <v>797798</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>8.649553921193789e-05</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -32869,7 +32869,7 @@
         <v>54878</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -32879,7 +32879,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>103893</v>
+        <v>103962</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>194866</v>
@@ -36418,7 +36418,7 @@
         <v>56598</v>
       </c>
       <c r="K94" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95">
@@ -39964,10 +39964,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>52805</v>
+        <v>52838</v>
       </c>
       <c r="K94" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95">
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52805</v>
+        <v>52838</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>759760</v>
+        <v>760552</v>
       </c>
       <c r="C94" t="n">
         <v>6421</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.01139864773888318</v>
+        <v>0.01244412880537948</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="95">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>138003</v>
+        <v>138795</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>339066</v>
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95">
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141204</v>
+        <v>141220</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141204</v>
+        <v>141220</v>
       </c>
     </row>
   </sheetData>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -22219,7 +22219,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>190104</v>
+        <v>190145</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22244,7 +22244,7 @@
         <v>154953</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190104</v>
+        <v>190145</v>
       </c>
     </row>
   </sheetData>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="95">
@@ -32842,13 +32842,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>797798</v>
+        <v>798019</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>8.649553921193789e-05</v>
+        <v>0.0003635319763979998</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -32869,7 +32869,7 @@
         <v>54878</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -32879,7 +32879,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>103962</v>
+        <v>104183</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>194866</v>
@@ -36418,7 +36418,7 @@
         <v>56598</v>
       </c>
       <c r="K94" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95">
@@ -39964,7 +39964,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>52838</v>
+        <v>52839</v>
       </c>
       <c r="K94" t="n">
         <v>87</v>
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52838</v>
+        <v>52839</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>321</v>
+        <v>346</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95">
@@ -15124,7 +15124,7 @@
         <v>141220</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>535369</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61650</v>
       </c>
       <c r="K94" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>516</v>
+        <v>529</v>
       </c>
     </row>
     <row r="95">
@@ -32869,7 +32869,7 @@
         <v>54878</v>
       </c>
       <c r="K94" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
@@ -36418,7 +36418,7 @@
         <v>56598</v>
       </c>
       <c r="K94" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>346</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95">
@@ -15124,7 +15124,7 @@
         <v>141220</v>
       </c>
       <c r="K94" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95">
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61650</v>
       </c>
       <c r="K94" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="95">
@@ -32869,7 +32869,7 @@
         <v>54878</v>
       </c>
       <c r="K94" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
@@ -36418,7 +36418,7 @@
         <v>56598</v>
       </c>
       <c r="K94" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95">
@@ -39967,7 +39967,7 @@
         <v>52839</v>
       </c>
       <c r="K94" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95">
@@ -15124,7 +15124,7 @@
         <v>141220</v>
       </c>
       <c r="K94" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95">
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95">
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61650</v>
       </c>
       <c r="K94" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="95">
@@ -32869,7 +32869,7 @@
         <v>54878</v>
       </c>
       <c r="K94" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95">
@@ -36418,7 +36418,7 @@
         <v>56598</v>
       </c>
       <c r="K94" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95">
@@ -39967,7 +39967,7 @@
         <v>52839</v>
       </c>
       <c r="K94" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="95">
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141220</v>
+        <v>141395</v>
       </c>
       <c r="K94" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141220</v>
+        <v>141395</v>
       </c>
     </row>
   </sheetData>
@@ -18658,22 +18658,22 @@
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>535369</v>
+        <v>535428</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>246998</v>
+        <v>220158</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>-0.03423073825966586</v>
       </c>
       <c r="J94" t="n">
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95">
@@ -18686,13 +18686,13 @@
         <v>89269</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>300512</v>
+        <v>300571</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>246998</v>
+        <v>220158</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>79734</v>
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95">
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61650</v>
+        <v>61649</v>
       </c>
       <c r="K94" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95">
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61650</v>
+        <v>61649</v>
       </c>
     </row>
   </sheetData>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>543</v>
+        <v>551</v>
       </c>
     </row>
     <row r="95">
@@ -32854,22 +32854,22 @@
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>301273</v>
+        <v>304419</v>
       </c>
       <c r="G94" t="n">
         <v>83</v>
       </c>
       <c r="H94" t="n">
-        <v>51058</v>
+        <v>51068</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>0.008955376347137174</v>
       </c>
       <c r="J94" t="n">
-        <v>54878</v>
+        <v>54903</v>
       </c>
       <c r="K94" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -32882,16 +32882,16 @@
         <v>104183</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>194866</v>
+        <v>198012</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>83</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>51058</v>
+        <v>51068</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54878</v>
+        <v>54903</v>
       </c>
     </row>
   </sheetData>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56598</v>
+        <v>56595</v>
       </c>
       <c r="K94" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56598</v>
+        <v>56595</v>
       </c>
     </row>
   </sheetData>
@@ -39964,10 +39964,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>52839</v>
+        <v>52865</v>
       </c>
       <c r="K94" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95">
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52839</v>
+        <v>52865</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95">
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141395</v>
+        <v>141417</v>
       </c>
       <c r="K94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141395</v>
+        <v>141417</v>
       </c>
     </row>
   </sheetData>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0001232579805540526</v>
       </c>
       <c r="E94" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61649</v>
       </c>
       <c r="K94" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="95">
@@ -32851,10 +32851,10 @@
         <v>0.0003635319763979998</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>304419</v>
+        <v>304493</v>
       </c>
       <c r="G94" t="n">
         <v>83</v>
@@ -32863,13 +32863,13 @@
         <v>51068</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.008955376347137174</v>
+        <v>0.00916535665438944</v>
       </c>
       <c r="J94" t="n">
-        <v>54903</v>
+        <v>54904</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -32882,7 +32882,7 @@
         <v>104183</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>198012</v>
+        <v>198086</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>83</v>
@@ -32891,7 +32891,7 @@
         <v>51068</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54903</v>
+        <v>54904</v>
       </c>
     </row>
   </sheetData>
@@ -36400,7 +36400,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>358699</v>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56595</v>
+        <v>56596</v>
       </c>
       <c r="K94" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56595</v>
+        <v>56596</v>
       </c>
     </row>
   </sheetData>
@@ -39964,10 +39964,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>52865</v>
+        <v>52874</v>
       </c>
       <c r="K94" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="95">
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52865</v>
+        <v>52874</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95">
@@ -15097,16 +15097,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1748614</v>
+        <v>1749161</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.002194539728390604</v>
+        <v>0.002508045403874976</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141417</v>
+        <v>141436</v>
       </c>
       <c r="K94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>541263</v>
+        <v>541810</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>637182</v>
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141417</v>
+        <v>141436</v>
       </c>
     </row>
   </sheetData>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95">
@@ -22195,16 +22195,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3073223</v>
+        <v>3074255</v>
       </c>
       <c r="C94" t="n">
         <v>50692</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.0001232579805540526</v>
+        <v>0.000453653398558682</v>
       </c>
       <c r="E94" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F94" t="n">
         <v>1842767</v>
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>737402</v>
+        <v>738434</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>958303</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61649</v>
+        <v>61685</v>
       </c>
       <c r="K94" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95">
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61649</v>
+        <v>61685</v>
       </c>
     </row>
   </sheetData>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="95">
@@ -32869,7 +32869,7 @@
         <v>54904</v>
       </c>
       <c r="K94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -36418,7 +36418,7 @@
         <v>56596</v>
       </c>
       <c r="K94" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95">
@@ -39964,10 +39964,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>52874</v>
+        <v>52893</v>
       </c>
       <c r="K94" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95">
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52874</v>
+        <v>52893</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2032,7 +2032,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS --RDA e RCE</a:t>
+              <a:t>BOLSAO/TRES LAGOAS--RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2209,7 +2209,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS --ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/TRES LAGOAS--ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -7995,7 +7995,7 @@
         <v>0.01244412880537948</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>559727</v>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>406</v>
+        <v>430</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95">
@@ -15106,7 +15106,7 @@
         <v>0.002508045403874976</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141436</v>
+        <v>141448</v>
       </c>
       <c r="K94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141436</v>
+        <v>141448</v>
       </c>
     </row>
   </sheetData>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95">
@@ -22195,34 +22195,34 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3074255</v>
+        <v>3074500</v>
       </c>
       <c r="C94" t="n">
-        <v>50692</v>
+        <v>51167</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.000453653398558682</v>
+        <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F94" t="n">
-        <v>1842767</v>
+        <v>1773740</v>
       </c>
       <c r="G94" t="n">
         <v>123505</v>
       </c>
       <c r="H94" t="n">
-        <v>154953</v>
+        <v>155338</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>-0.03235960353097856</v>
       </c>
       <c r="J94" t="n">
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95">
@@ -22232,16 +22232,16 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>738434</v>
+        <v>738679</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>958303</v>
+        <v>889276</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>123505</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>154953</v>
+        <v>155338</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>190145</v>
@@ -25744,13 +25744,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>948503</v>
+        <v>948655</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>0.00016025252424083</v>
       </c>
       <c r="E94" t="n">
         <v>3</v>
@@ -25771,7 +25771,7 @@
         <v>61685</v>
       </c>
       <c r="K94" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95">
@@ -25781,7 +25781,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>219613</v>
+        <v>219765</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>358194</v>
@@ -29311,16 +29311,16 @@
         <v>6655</v>
       </c>
       <c r="H94" t="n">
-        <v>128398</v>
+        <v>130203</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>0.002792941671618142</v>
       </c>
       <c r="J94" t="n">
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>565</v>
+        <v>576</v>
       </c>
     </row>
     <row r="95">
@@ -29339,7 +29339,7 @@
         <v>6655</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>128398</v>
+        <v>130203</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>66062</v>
@@ -32851,7 +32851,7 @@
         <v>0.0003635319763979998</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>304493</v>
@@ -32869,7 +32869,7 @@
         <v>54904</v>
       </c>
       <c r="K94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56596</v>
+        <v>56595</v>
       </c>
       <c r="K94" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56596</v>
+        <v>56595</v>
       </c>
     </row>
   </sheetData>
@@ -39949,7 +39949,7 @@
         <v>0.001426411490868579</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>295759</v>
@@ -39967,7 +39967,7 @@
         <v>52893</v>
       </c>
       <c r="K94" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -2032,7 +2032,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS--RDA e RCE</a:t>
+              <a:t>BOLSAO/TRES LAGOAS --RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2209,7 +2209,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS--ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/TRES LAGOAS --ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -11544,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="95">
@@ -15124,7 +15124,7 @@
         <v>141448</v>
       </c>
       <c r="K94" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F94" t="n">
         <v>1773740</v>
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61685</v>
       </c>
       <c r="K94" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="95">
@@ -32869,7 +32869,7 @@
         <v>54904</v>
       </c>
       <c r="K94" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>430</v>
+        <v>449</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95">
@@ -15106,7 +15106,7 @@
         <v>0.002508045403874976</v>
       </c>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15124,7 +15124,7 @@
         <v>141448</v>
       </c>
       <c r="K94" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95">
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F94" t="n">
         <v>1773740</v>
@@ -22222,7 +22222,7 @@
         <v>190145</v>
       </c>
       <c r="K94" t="n">
-        <v>178</v>
+        <v>207</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61685</v>
       </c>
       <c r="K94" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>577</v>
+        <v>593</v>
       </c>
     </row>
     <row r="95">
@@ -32869,7 +32869,7 @@
         <v>54904</v>
       </c>
       <c r="K94" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -39967,7 +39967,7 @@
         <v>52893</v>
       </c>
       <c r="K94" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2032,7 +2032,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS --RDA e RCE</a:t>
+              <a:t>BOLSAO/TRES LAGOAS--RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2209,7 +2209,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS --ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/TRES LAGOAS--ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -7995,7 +7995,7 @@
         <v>0.01244412880537948</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
         <v>559727</v>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>449</v>
+        <v>465</v>
       </c>
     </row>
     <row r="95">
@@ -11544,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -11562,7 +11562,7 @@
         <v>79937</v>
       </c>
       <c r="K94" t="n">
-        <v>295</v>
+        <v>307</v>
       </c>
     </row>
     <row r="95">
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141448</v>
+        <v>141519</v>
       </c>
       <c r="K94" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141448</v>
+        <v>141519</v>
       </c>
     </row>
   </sheetData>
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F94" t="n">
         <v>1773740</v>
@@ -22219,10 +22219,10 @@
         <v>-0.03235960353097856</v>
       </c>
       <c r="J94" t="n">
-        <v>190145</v>
+        <v>190181</v>
       </c>
       <c r="K94" t="n">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95">
@@ -22244,7 +22244,7 @@
         <v>155338</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190145</v>
+        <v>190181</v>
       </c>
     </row>
   </sheetData>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61685</v>
+        <v>61737</v>
       </c>
       <c r="K94" t="n">
-        <v>141</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95">
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61685</v>
+        <v>61737</v>
       </c>
     </row>
   </sheetData>
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>511219</v>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="95">
@@ -32851,7 +32851,7 @@
         <v>0.0003635319763979998</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
         <v>304493</v>
@@ -32869,7 +32869,7 @@
         <v>54904</v>
       </c>
       <c r="K94" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
@@ -36400,7 +36400,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>358699</v>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56595</v>
+        <v>56609</v>
       </c>
       <c r="K94" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56595</v>
+        <v>56609</v>
       </c>
     </row>
   </sheetData>
@@ -39964,10 +39964,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>52893</v>
+        <v>52896</v>
       </c>
       <c r="K94" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95">
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52893</v>
+        <v>52896</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2032,7 +2032,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS--RDA e RCE</a:t>
+              <a:t>BOLSAO/TRES LAGOAS --RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2209,7 +2209,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/TRES LAGOAS--ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/TRES LAGOAS --ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>465</v>
+        <v>499</v>
       </c>
     </row>
     <row r="95">
@@ -11535,16 +11535,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1077298</v>
+        <v>1078669</v>
       </c>
       <c r="C94" t="n">
         <v>6373</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>0.001265144125846313</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>750284</v>
@@ -11559,10 +11559,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>79937</v>
+        <v>80004</v>
       </c>
       <c r="K94" t="n">
-        <v>307</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>227872</v>
+        <v>229243</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>251377</v>
@@ -11584,7 +11584,7 @@
         <v>94589</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>79937</v>
+        <v>80004</v>
       </c>
     </row>
   </sheetData>
@@ -15106,7 +15106,7 @@
         <v>0.002508045403874976</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141519</v>
+        <v>141529</v>
       </c>
       <c r="K94" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141519</v>
+        <v>141529</v>
       </c>
     </row>
   </sheetData>
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95">
@@ -22204,25 +22204,25 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F94" t="n">
-        <v>1773740</v>
+        <v>1774291</v>
       </c>
       <c r="G94" t="n">
         <v>123505</v>
       </c>
       <c r="H94" t="n">
-        <v>155338</v>
+        <v>159781</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.03235960353097856</v>
+        <v>-0.03000530353922851</v>
       </c>
       <c r="J94" t="n">
-        <v>190181</v>
+        <v>190313</v>
       </c>
       <c r="K94" t="n">
-        <v>191</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95">
@@ -22235,16 +22235,16 @@
         <v>738679</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>889276</v>
+        <v>889827</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>123505</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>155338</v>
+        <v>159781</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190181</v>
+        <v>190313</v>
       </c>
     </row>
   </sheetData>
@@ -25744,13 +25744,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>948655</v>
+        <v>948696</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.00016025252424083</v>
+        <v>0.0002034785340689486</v>
       </c>
       <c r="E94" t="n">
         <v>3</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61737</v>
+        <v>61744</v>
       </c>
       <c r="K94" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95">
@@ -25781,7 +25781,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>219765</v>
+        <v>219806</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>358194</v>
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61737</v>
+        <v>61744</v>
       </c>
     </row>
   </sheetData>
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>511219</v>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>596</v>
+        <v>605</v>
       </c>
     </row>
     <row r="95">
@@ -32842,16 +32842,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>798019</v>
+        <v>798009</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.0003635319763979998</v>
+        <v>0.0003509963910049653</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>304493</v>
@@ -32866,10 +32866,10 @@
         <v>0.00916535665438944</v>
       </c>
       <c r="J94" t="n">
-        <v>54904</v>
+        <v>54922</v>
       </c>
       <c r="K94" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -32879,7 +32879,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>104183</v>
+        <v>104173</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>198086</v>
@@ -32891,7 +32891,7 @@
         <v>51068</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54904</v>
+        <v>54922</v>
       </c>
     </row>
   </sheetData>
@@ -36400,7 +36400,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>358699</v>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56609</v>
+        <v>56637</v>
       </c>
       <c r="K94" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56609</v>
+        <v>56637</v>
       </c>
     </row>
   </sheetData>
@@ -39967,7 +39967,7 @@
         <v>52896</v>
       </c>
       <c r="K94" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>499</v>
+        <v>513</v>
       </c>
     </row>
     <row r="95">
@@ -11562,7 +11562,7 @@
         <v>80004</v>
       </c>
       <c r="K94" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95">
@@ -15106,7 +15106,7 @@
         <v>0.002508045403874976</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141529</v>
+        <v>141545</v>
       </c>
       <c r="K94" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141529</v>
+        <v>141545</v>
       </c>
     </row>
   </sheetData>
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22222,7 +22222,7 @@
         <v>190313</v>
       </c>
       <c r="K94" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95">
@@ -25753,7 +25753,7 @@
         <v>0.0002034785340689486</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
         <v>590365</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61744</v>
+        <v>44467</v>
       </c>
       <c r="K94" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95">
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61744</v>
+        <v>44467</v>
       </c>
     </row>
   </sheetData>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="95">
@@ -32851,7 +32851,7 @@
         <v>0.0003509963910049653</v>
       </c>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>304493</v>
@@ -32866,10 +32866,10 @@
         <v>0.00916535665438944</v>
       </c>
       <c r="J94" t="n">
-        <v>54922</v>
+        <v>54927</v>
       </c>
       <c r="K94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -32891,7 +32891,7 @@
         <v>51068</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54922</v>
+        <v>54927</v>
       </c>
     </row>
   </sheetData>
@@ -36400,7 +36400,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>358699</v>
@@ -36418,7 +36418,7 @@
         <v>56637</v>
       </c>
       <c r="K94" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95">
@@ -39949,7 +39949,7 @@
         <v>0.001426411490868579</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>295759</v>
@@ -39967,7 +39967,7 @@
         <v>52896</v>
       </c>
       <c r="K94" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7995,7 +7995,7 @@
         <v>0.01244412880537948</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>559727</v>
@@ -11544,25 +11544,25 @@
         <v>0.001265144125846313</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
-        <v>750284</v>
+        <v>772857</v>
       </c>
       <c r="G94" t="n">
         <v>26677</v>
       </c>
       <c r="H94" t="n">
-        <v>94589</v>
+        <v>95862</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>0.02736044977339223</v>
       </c>
       <c r="J94" t="n">
         <v>80004</v>
       </c>
       <c r="K94" t="n">
-        <v>257</v>
+        <v>284</v>
       </c>
     </row>
     <row r="95">
@@ -11575,13 +11575,13 @@
         <v>229243</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>251377</v>
+        <v>273950</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>26677</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>94589</v>
+        <v>95862</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>80004</v>
@@ -15106,7 +15106,7 @@
         <v>0.002508045403874976</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>1179778</v>
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>141545</v>
+        <v>141558</v>
       </c>
       <c r="K94" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>134808</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141545</v>
+        <v>141558</v>
       </c>
     </row>
   </sheetData>
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22219,10 +22219,10 @@
         <v>-0.03000530353922851</v>
       </c>
       <c r="J94" t="n">
-        <v>190313</v>
+        <v>190325</v>
       </c>
       <c r="K94" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95">
@@ -22244,7 +22244,7 @@
         <v>159781</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190313</v>
+        <v>190325</v>
       </c>
     </row>
   </sheetData>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>44467</v>
+        <v>61788</v>
       </c>
       <c r="K94" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95">
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>44467</v>
+        <v>61788</v>
       </c>
     </row>
   </sheetData>
@@ -29320,7 +29320,7 @@
         <v>66062</v>
       </c>
       <c r="K94" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="95">
@@ -32851,7 +32851,7 @@
         <v>0.0003509963910049653</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F94" t="n">
         <v>304493</v>
@@ -32866,10 +32866,10 @@
         <v>0.00916535665438944</v>
       </c>
       <c r="J94" t="n">
-        <v>54927</v>
+        <v>54929</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -32891,7 +32891,7 @@
         <v>51068</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54927</v>
+        <v>54929</v>
       </c>
     </row>
   </sheetData>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56637</v>
+        <v>56634</v>
       </c>
       <c r="K94" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56637</v>
+        <v>56634</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7995,7 +7995,7 @@
         <v>0.01244412880537948</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F94" t="n">
         <v>559727</v>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="95">
@@ -11544,7 +11544,7 @@
         <v>0.001265144125846313</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F94" t="n">
         <v>772857</v>
@@ -11562,7 +11562,7 @@
         <v>80004</v>
       </c>
       <c r="K94" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="95">
@@ -15097,34 +15097,34 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1749161</v>
+        <v>1749446</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.002508045403874976</v>
+        <v>0.002671389311577071</v>
       </c>
       <c r="E94" t="n">
         <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>1179778</v>
+        <v>1181735</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>134808</v>
+        <v>137678</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>0.003671878446902675</v>
       </c>
       <c r="J94" t="n">
-        <v>141558</v>
+        <v>141565</v>
       </c>
       <c r="K94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -15134,19 +15134,19 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>541810</v>
+        <v>542095</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>637182</v>
+        <v>639139</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>134808</v>
+        <v>137678</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141558</v>
+        <v>141565</v>
       </c>
     </row>
   </sheetData>
@@ -18646,16 +18646,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1219332</v>
+        <v>1219348</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>1.312193889769152e-05</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95">
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>89269</v>
+        <v>89285</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>300571</v>
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22213,16 +22213,16 @@
         <v>123505</v>
       </c>
       <c r="H94" t="n">
-        <v>159781</v>
+        <v>160568</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.03000530353922851</v>
+        <v>-0.02963429150608728</v>
       </c>
       <c r="J94" t="n">
         <v>190325</v>
       </c>
       <c r="K94" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
     </row>
     <row r="95">
@@ -22241,7 +22241,7 @@
         <v>123505</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>159781</v>
+        <v>160568</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>190325</v>
@@ -25768,7 +25768,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61788</v>
+        <v>61804</v>
       </c>
       <c r="K94" t="n">
         <v>96</v>
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61788</v>
+        <v>61804</v>
       </c>
     </row>
   </sheetData>
@@ -29317,10 +29317,10 @@
         <v>0.002792941671618142</v>
       </c>
       <c r="J94" t="n">
-        <v>66062</v>
+        <v>66105</v>
       </c>
       <c r="K94" t="n">
-        <v>613</v>
+        <v>586</v>
       </c>
     </row>
     <row r="95">
@@ -29342,7 +29342,7 @@
         <v>130203</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>66062</v>
+        <v>66105</v>
       </c>
     </row>
   </sheetData>
@@ -32851,25 +32851,25 @@
         <v>0.0003509963910049653</v>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>304493</v>
+        <v>305908</v>
       </c>
       <c r="G94" t="n">
         <v>83</v>
       </c>
       <c r="H94" t="n">
-        <v>51068</v>
+        <v>77381</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.00916535665438944</v>
+        <v>0.08784554529615736</v>
       </c>
       <c r="J94" t="n">
-        <v>54929</v>
+        <v>54935</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -32882,16 +32882,16 @@
         <v>104173</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>198086</v>
+        <v>199501</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>83</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>51068</v>
+        <v>77381</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54929</v>
+        <v>54935</v>
       </c>
     </row>
   </sheetData>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56634</v>
+        <v>56707</v>
       </c>
       <c r="K94" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56634</v>
+        <v>56707</v>
       </c>
     </row>
   </sheetData>
@@ -39952,7 +39952,7 @@
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>295759</v>
+        <v>288478</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -39961,13 +39961,13 @@
         <v>72</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>-0.02461202510893044</v>
       </c>
       <c r="J94" t="n">
-        <v>52896</v>
+        <v>52915</v>
       </c>
       <c r="K94" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95">
@@ -39980,7 +39980,7 @@
         <v>-107348</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>-7808</v>
+        <v>-15089</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>0</v>
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52896</v>
+        <v>52915</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="95">
@@ -11544,7 +11544,7 @@
         <v>0.001265144125846313</v>
       </c>
       <c r="E94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F94" t="n">
         <v>772857</v>
@@ -11562,7 +11562,7 @@
         <v>80004</v>
       </c>
       <c r="K94" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95">
@@ -15124,7 +15124,7 @@
         <v>141565</v>
       </c>
       <c r="K94" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -18673,7 +18673,7 @@
         <v>79734</v>
       </c>
       <c r="K94" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95">
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22222,7 +22222,7 @@
         <v>190325</v>
       </c>
       <c r="K94" t="n">
-        <v>135</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61804</v>
       </c>
       <c r="K94" t="n">
-        <v>96</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66105</v>
       </c>
       <c r="K94" t="n">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="95">
@@ -32851,7 +32851,7 @@
         <v>0.0003509963910049653</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F94" t="n">
         <v>305908</v>
@@ -32869,7 +32869,7 @@
         <v>54935</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -36418,7 +36418,7 @@
         <v>56707</v>
       </c>
       <c r="K94" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95">
@@ -39967,7 +39967,7 @@
         <v>52915</v>
       </c>
       <c r="K94" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -165,7 +165,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--RDA e RCE</a:t>
+              <a:t>BOLSAO/PARANAIBA --RDA e RCE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1802,7 +1802,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BOLSAO/PARANAIBA--ECON e PENDENTES</a:t>
+              <a:t>BOLSAO/PARANAIBA --ECON e PENDENTES</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -8013,7 +8013,7 @@
         <v>69791</v>
       </c>
       <c r="K94" t="n">
-        <v>533</v>
+        <v>544</v>
       </c>
     </row>
     <row r="95">
@@ -15124,7 +15124,7 @@
         <v>141565</v>
       </c>
       <c r="K94" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
@@ -22222,7 +22222,7 @@
         <v>190325</v>
       </c>
       <c r="K94" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95">
@@ -25771,7 +25771,7 @@
         <v>61804</v>
       </c>
       <c r="K94" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95">
@@ -29320,7 +29320,7 @@
         <v>66105</v>
       </c>
       <c r="K94" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="95">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7995,19 +7995,19 @@
         <v>0.01244412880537948</v>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>559727</v>
+        <v>559784</v>
       </c>
       <c r="G94" t="n">
         <v>14163</v>
       </c>
       <c r="H94" t="n">
-        <v>37774</v>
+        <v>38566</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.0005430764298286365</v>
+        <v>0.001931847179601264</v>
       </c>
       <c r="J94" t="n">
         <v>69791</v>
@@ -8026,13 +8026,13 @@
         <v>138795</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>339066</v>
+        <v>339123</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>14163</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>37774</v>
+        <v>38566</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>69791</v>
@@ -11559,10 +11559,10 @@
         <v>0.02736044977339223</v>
       </c>
       <c r="J94" t="n">
-        <v>80004</v>
+        <v>80083</v>
       </c>
       <c r="K94" t="n">
-        <v>302</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95">
@@ -11584,7 +11584,7 @@
         <v>95862</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>80004</v>
+        <v>80083</v>
       </c>
     </row>
   </sheetData>
@@ -15106,7 +15106,7 @@
         <v>0.002671389311577071</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
         <v>1181735</v>
@@ -15121,10 +15121,10 @@
         <v>0.003671878446902675</v>
       </c>
       <c r="J94" t="n">
-        <v>141565</v>
+        <v>141592</v>
       </c>
       <c r="K94" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -15146,7 +15146,7 @@
         <v>137678</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141565</v>
+        <v>141592</v>
       </c>
     </row>
   </sheetData>
@@ -18646,16 +18646,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1219348</v>
+        <v>1219577</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>1.312193889769152e-05</v>
+        <v>0.0002009296893709015</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>89285</v>
+        <v>89514</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>300571</v>
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -25753,7 +25753,7 @@
         <v>0.0002034785340689486</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>590365</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>61804</v>
+        <v>61845</v>
       </c>
       <c r="K94" t="n">
-        <v>140</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95">
@@ -25793,7 +25793,7 @@
         <v>80609</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>61804</v>
+        <v>61845</v>
       </c>
     </row>
   </sheetData>
@@ -32866,10 +32866,10 @@
         <v>0.08784554529615736</v>
       </c>
       <c r="J94" t="n">
-        <v>54935</v>
+        <v>54937</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -32891,7 +32891,7 @@
         <v>77381</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54935</v>
+        <v>54937</v>
       </c>
     </row>
   </sheetData>
@@ -36415,10 +36415,10 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56707</v>
+        <v>56753</v>
       </c>
       <c r="K94" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56707</v>
+        <v>56753</v>
       </c>
     </row>
   </sheetData>
@@ -39964,10 +39964,10 @@
         <v>-0.02461202510893044</v>
       </c>
       <c r="J94" t="n">
-        <v>52915</v>
+        <v>52918</v>
       </c>
       <c r="K94" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95">
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52915</v>
+        <v>52918</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7986,16 +7986,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>760552</v>
+        <v>761112</v>
       </c>
       <c r="C94" t="n">
         <v>6421</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.01244412880537948</v>
+        <v>0.01318335784229605</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F94" t="n">
         <v>559784</v>
@@ -8004,10 +8004,10 @@
         <v>14163</v>
       </c>
       <c r="H94" t="n">
-        <v>38566</v>
+        <v>38634</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.001931847179601264</v>
+        <v>0.002043079701373394</v>
       </c>
       <c r="J94" t="n">
         <v>69791</v>
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>138795</v>
+        <v>139355</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>339123</v>
@@ -8032,7 +8032,7 @@
         <v>14163</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>38566</v>
+        <v>38634</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>69791</v>
@@ -11544,7 +11544,7 @@
         <v>0.001265144125846313</v>
       </c>
       <c r="E94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F94" t="n">
         <v>772857</v>
@@ -15106,7 +15106,7 @@
         <v>0.002671389311577071</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>1181735</v>
@@ -18655,7 +18655,7 @@
         <v>0.0002009296893709015</v>
       </c>
       <c r="E94" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22219,10 +22219,10 @@
         <v>-0.02963429150608728</v>
       </c>
       <c r="J94" t="n">
-        <v>190325</v>
+        <v>190404</v>
       </c>
       <c r="K94" t="n">
-        <v>178</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95">
@@ -22244,7 +22244,7 @@
         <v>160568</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190325</v>
+        <v>190404</v>
       </c>
     </row>
   </sheetData>
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
         <v>511219</v>
@@ -32851,7 +32851,7 @@
         <v>0.0003509963910049653</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F94" t="n">
         <v>305908</v>
@@ -32866,10 +32866,10 @@
         <v>0.08784554529615736</v>
       </c>
       <c r="J94" t="n">
-        <v>54937</v>
+        <v>54938</v>
       </c>
       <c r="K94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -32891,7 +32891,7 @@
         <v>77381</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54937</v>
+        <v>54938</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>761112</v>
+        <v>761114</v>
       </c>
       <c r="C94" t="n">
         <v>6421</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.01318335784229605</v>
+        <v>0.01318599794599932</v>
       </c>
       <c r="E94" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
         <v>0.002043079701373394</v>
       </c>
       <c r="J94" t="n">
-        <v>69791</v>
+        <v>69823</v>
       </c>
       <c r="K94" t="n">
-        <v>544</v>
+        <v>512</v>
       </c>
     </row>
     <row r="95">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>139355</v>
+        <v>139357</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>339123</v>
@@ -8035,7 +8035,7 @@
         <v>38634</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>69791</v>
+        <v>69823</v>
       </c>
     </row>
   </sheetData>
@@ -11544,7 +11544,7 @@
         <v>0.001265144125846313</v>
       </c>
       <c r="E94" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F94" t="n">
         <v>772857</v>
@@ -18646,16 +18646,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1219577</v>
+        <v>1219549</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.0002009296893709015</v>
+        <v>0.0001779662962999413</v>
       </c>
       <c r="E94" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>89514</v>
+        <v>89486</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>300571</v>
@@ -22204,7 +22204,7 @@
         <v>0.0006841618297247025</v>
       </c>
       <c r="E94" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22219,10 +22219,10 @@
         <v>-0.02963429150608728</v>
       </c>
       <c r="J94" t="n">
-        <v>190404</v>
+        <v>190468</v>
       </c>
       <c r="K94" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
@@ -22244,7 +22244,7 @@
         <v>160568</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190404</v>
+        <v>190468</v>
       </c>
     </row>
   </sheetData>
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>511219</v>
@@ -39964,10 +39964,10 @@
         <v>-0.02461202510893044</v>
       </c>
       <c r="J94" t="n">
-        <v>52918</v>
+        <v>52952</v>
       </c>
       <c r="K94" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95">
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52918</v>
+        <v>52952</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>761114</v>
+        <v>760748</v>
       </c>
       <c r="C94" t="n">
         <v>6421</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.01318599794599932</v>
+        <v>0.01270285896830027</v>
       </c>
       <c r="E94" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
         <v>0.002043079701373394</v>
       </c>
       <c r="J94" t="n">
-        <v>69823</v>
+        <v>69837</v>
       </c>
       <c r="K94" t="n">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>139357</v>
+        <v>138991</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>339123</v>
@@ -8035,7 +8035,7 @@
         <v>38634</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>69823</v>
+        <v>69837</v>
       </c>
     </row>
   </sheetData>
@@ -18655,7 +18655,7 @@
         <v>0.0001779662962999413</v>
       </c>
       <c r="E94" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -22195,16 +22195,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3074500</v>
+        <v>3074588</v>
       </c>
       <c r="C94" t="n">
-        <v>51167</v>
+        <v>60572</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.0006841618297247025</v>
+        <v>0.003723351464528914</v>
       </c>
       <c r="E94" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22219,10 +22219,10 @@
         <v>-0.02963429150608728</v>
       </c>
       <c r="J94" t="n">
-        <v>190468</v>
+        <v>190502</v>
       </c>
       <c r="K94" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>738679</v>
+        <v>738767</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>889827</v>
@@ -22244,7 +22244,7 @@
         <v>160568</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190468</v>
+        <v>190502</v>
       </c>
     </row>
   </sheetData>
@@ -32851,7 +32851,7 @@
         <v>0.0003509963910049653</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>305908</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -15121,7 +15121,7 @@
         <v>0.003671878446902675</v>
       </c>
       <c r="J94" t="n">
-        <v>141592</v>
+        <v>141591</v>
       </c>
       <c r="K94" t="n">
         <v>2</v>
@@ -15146,7 +15146,7 @@
         <v>137678</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>141592</v>
+        <v>141591</v>
       </c>
     </row>
   </sheetData>
@@ -18655,7 +18655,7 @@
         <v>0.0001779662962999413</v>
       </c>
       <c r="E94" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F94" t="n">
         <v>535428</v>
@@ -22204,7 +22204,7 @@
         <v>0.003723351464528914</v>
       </c>
       <c r="E94" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F94" t="n">
         <v>1774291</v>
@@ -22219,7 +22219,7 @@
         <v>-0.02963429150608728</v>
       </c>
       <c r="J94" t="n">
-        <v>190502</v>
+        <v>190511</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22244,7 +22244,7 @@
         <v>160568</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>190502</v>
+        <v>190511</v>
       </c>
     </row>
   </sheetData>
@@ -29317,7 +29317,7 @@
         <v>0.002792941671618142</v>
       </c>
       <c r="J94" t="n">
-        <v>66105</v>
+        <v>66104</v>
       </c>
       <c r="K94" t="n">
         <v>593</v>
@@ -29342,7 +29342,7 @@
         <v>130203</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>66105</v>
+        <v>66104</v>
       </c>
     </row>
   </sheetData>
@@ -32866,7 +32866,7 @@
         <v>0.08784554529615736</v>
       </c>
       <c r="J94" t="n">
-        <v>54938</v>
+        <v>54935</v>
       </c>
       <c r="K94" t="n">
         <v>2</v>
@@ -32891,7 +32891,7 @@
         <v>77381</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>54938</v>
+        <v>54935</v>
       </c>
     </row>
   </sheetData>
@@ -36415,7 +36415,7 @@
         <v>0.0001393260746168533</v>
       </c>
       <c r="J94" t="n">
-        <v>56753</v>
+        <v>56752</v>
       </c>
       <c r="K94" t="n">
         <v>34</v>
@@ -36440,7 +36440,7 @@
         <v>28935</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>56753</v>
+        <v>56752</v>
       </c>
     </row>
   </sheetData>
@@ -39964,7 +39964,7 @@
         <v>-0.02461202510893044</v>
       </c>
       <c r="J94" t="n">
-        <v>52952</v>
+        <v>52944</v>
       </c>
       <c r="K94" t="n">
         <v>48</v>
@@ -39989,7 +39989,7 @@
         <v>72</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>52952</v>
+        <v>52944</v>
       </c>
     </row>
   </sheetData>
